--- a/data/bist_screener_2026-05-20.xlsx
+++ b/data/bist_screener_2026-05-20.xlsx
@@ -3017,42 +3017,42 @@
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>CANTE</t>
+          <t>BAGFS</t>
         </is>
       </c>
       <c r="B59" s="7" t="n">
-        <v>1.57</v>
+        <v>29.86</v>
       </c>
       <c r="C59" s="8" t="n">
-        <v>0</v>
+        <v>-0.0368</v>
       </c>
       <c r="D59" s="9" t="n">
-        <v>771440000</v>
+        <v>4620000</v>
       </c>
       <c r="E59" s="8" t="n">
-        <v>0.7071</v>
+        <v>0.5611</v>
       </c>
       <c r="F59" s="7" t="n">
-        <v>36.37</v>
+        <v>34.08</v>
       </c>
       <c r="G59" s="6" t="inlineStr"/>
       <c r="H59" s="7" t="n">
         <v>0.5</v>
       </c>
       <c r="I59" s="8" t="n">
-        <v>-0.07969999999999999</v>
+        <v>-0.0416</v>
       </c>
       <c r="J59" s="8" t="n">
-        <v>-1.8045</v>
+        <v>-1.0319</v>
       </c>
       <c r="K59" s="6" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="L59" s="6" t="inlineStr">
         <is>
-          <t>BIST 100, BIST ELEKTRIK, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST 50, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KURUMSAL YÖNETİM, BIST KATILIM 30, BIST 50-30, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ, BIST 50-30 AGIRLIK SINIRLAMALI 25, BIST 50-30 AĞIRLIK SINIRLAMALI 10</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST BALIKESİR</t>
         </is>
       </c>
       <c r="M59" s="6" t="inlineStr"/>
@@ -3060,44 +3060,42 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>KRTEK</t>
+          <t>CANTE</t>
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>24.46</v>
+        <v>1.57</v>
       </c>
       <c r="C60" s="4" t="n">
-        <v>-0.0145</v>
+        <v>0</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>326570</v>
+        <v>771440000</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>0.8442000000000001</v>
+        <v>0.7071</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>43.91</v>
-      </c>
-      <c r="G60" s="3" t="n">
-        <v>54.01</v>
-      </c>
+        <v>36.37</v>
+      </c>
+      <c r="G60" s="2" t="inlineStr"/>
       <c r="H60" s="3" t="n">
         <v>0.5</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>0.0106</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="J60" s="4" t="n">
-        <v>-1.6389</v>
+        <v>-1.8045</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TEKSTİL DERİ, BIST KAYSERİ</t>
+          <t>BIST 100, BIST ELEKTRIK, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST 50, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KURUMSAL YÖNETİM, BIST KATILIM 30, BIST 50-30, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ, BIST 50-30 AGIRLIK SINIRLAMALI 25, BIST 50-30 AĞIRLIK SINIRLAMALI 10</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr"/>
@@ -3105,44 +3103,44 @@
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>SAHOL</t>
+          <t>KRTEK</t>
         </is>
       </c>
       <c r="B61" s="7" t="n">
-        <v>92.65000000000001</v>
+        <v>24.46</v>
       </c>
       <c r="C61" s="8" t="n">
-        <v>0.0038</v>
+        <v>-0.0145</v>
       </c>
       <c r="D61" s="9" t="n">
-        <v>30800000</v>
+        <v>326570</v>
       </c>
       <c r="E61" s="8" t="n">
-        <v>0.654</v>
+        <v>0.8442000000000001</v>
       </c>
       <c r="F61" s="7" t="n">
-        <v>41.01</v>
+        <v>43.91</v>
       </c>
       <c r="G61" s="7" t="n">
-        <v>26.47</v>
+        <v>54.01</v>
       </c>
       <c r="H61" s="7" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="I61" s="8" t="n">
-        <v>0.0218</v>
+        <v>0.0106</v>
       </c>
       <c r="J61" s="8" t="n">
-        <v>-0.9307</v>
+        <v>-1.6389</v>
       </c>
       <c r="K61" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="L61" s="6" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 30, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST HOLDING VE YATIRIM, BIST 50, BIST MALİ, BIST İSTANBUL, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25, STOXX Emerging Markets 1500, STOXX Eastern Europe 50</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TEKSTİL DERİ, BIST KAYSERİ</t>
         </is>
       </c>
       <c r="M61" s="6" t="inlineStr"/>
@@ -3150,42 +3148,44 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>ULUUN</t>
+          <t>SAHOL</t>
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>9.380000000000001</v>
+        <v>92.65000000000001</v>
       </c>
       <c r="C62" s="4" t="n">
-        <v>0.0229</v>
-      </c>
-      <c r="D62" s="3" t="n">
-        <v>16490000</v>
+        <v>0.0038</v>
+      </c>
+      <c r="D62" s="5" t="n">
+        <v>30800000</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>0.3219</v>
+        <v>0.654</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>57.55</v>
-      </c>
-      <c r="G62" s="2" t="inlineStr"/>
+        <v>41.01</v>
+      </c>
+      <c r="G62" s="3" t="n">
+        <v>26.47</v>
+      </c>
       <c r="H62" s="3" t="n">
         <v>0.51</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>-0.0068</v>
+        <v>0.0218</v>
       </c>
       <c r="J62" s="4" t="n">
-        <v>2.0381</v>
+        <v>-0.9307</v>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST ANA</t>
+          <t>BIST 100, BIST 30, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST HOLDING VE YATIRIM, BIST 50, BIST MALİ, BIST İSTANBUL, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25, STOXX Emerging Markets 1500, STOXX Eastern Europe 50</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr"/>
@@ -3193,44 +3193,42 @@
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>DZGYO</t>
+          <t>ULUUN</t>
         </is>
       </c>
       <c r="B63" s="7" t="n">
-        <v>7.96</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="C63" s="8" t="n">
-        <v>-0.0025</v>
-      </c>
-      <c r="D63" s="9" t="n">
-        <v>3810000</v>
+        <v>0.0229</v>
+      </c>
+      <c r="D63" s="7" t="n">
+        <v>16490000</v>
       </c>
       <c r="E63" s="8" t="n">
-        <v>0.2805</v>
+        <v>0.3219</v>
       </c>
       <c r="F63" s="7" t="n">
-        <v>48.98</v>
-      </c>
-      <c r="G63" s="7" t="n">
-        <v>10.29</v>
-      </c>
+        <v>57.55</v>
+      </c>
+      <c r="G63" s="6" t="inlineStr"/>
       <c r="H63" s="7" t="n">
         <v>0.51</v>
       </c>
       <c r="I63" s="8" t="n">
-        <v>0.0575</v>
+        <v>-0.0068</v>
       </c>
       <c r="J63" s="8" t="n">
-        <v>-0.9752</v>
+        <v>2.0381</v>
       </c>
       <c r="K63" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="L63" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST ANA</t>
+          <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M63" s="6" t="inlineStr"/>
@@ -3238,35 +3236,35 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>KZBGY</t>
+          <t>DZGYO</t>
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>3.11</v>
+        <v>7.96</v>
       </c>
       <c r="C64" s="4" t="n">
-        <v>-0.009599999999999999</v>
+        <v>-0.0025</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>76600000</v>
+        <v>3810000</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>0.348</v>
+        <v>0.2805</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>39.43</v>
+        <v>48.98</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>15.6</v>
+        <v>10.29</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>0.038</v>
+        <v>0.0575</v>
       </c>
       <c r="J64" s="4" t="n">
-        <v>-0.8970999999999999</v>
+        <v>-0.9752</v>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
@@ -3275,7 +3273,7 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST KATILIM 50</t>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST ANA</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr"/>
@@ -3283,44 +3281,44 @@
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>YATAS</t>
+          <t>KZBGY</t>
         </is>
       </c>
       <c r="B65" s="7" t="n">
-        <v>42.86</v>
+        <v>3.11</v>
       </c>
       <c r="C65" s="8" t="n">
-        <v>-0.0369</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="D65" s="9" t="n">
-        <v>3770000</v>
+        <v>76600000</v>
       </c>
       <c r="E65" s="8" t="n">
-        <v>0.7472</v>
+        <v>0.348</v>
       </c>
       <c r="F65" s="7" t="n">
-        <v>46.12</v>
+        <v>39.43</v>
       </c>
       <c r="G65" s="7" t="n">
-        <v>33.75</v>
+        <v>15.6</v>
       </c>
       <c r="H65" s="7" t="n">
         <v>0.52</v>
       </c>
       <c r="I65" s="8" t="n">
-        <v>0.0178</v>
+        <v>0.038</v>
       </c>
       <c r="J65" s="8" t="n">
-        <v>-0.9085</v>
+        <v>-0.8970999999999999</v>
       </c>
       <c r="K65" s="6" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L65" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TEKSTİL DERİ, BIST KATILIM TÜM, BIST ANA, BIST KAYSERİ</t>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST KATILIM 50</t>
         </is>
       </c>
       <c r="M65" s="6" t="inlineStr"/>
@@ -3328,44 +3326,44 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>MSGYO</t>
+          <t>YATAS</t>
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>6.01</v>
+        <v>42.86</v>
       </c>
       <c r="C66" s="4" t="n">
-        <v>-0.005</v>
+        <v>-0.0369</v>
       </c>
       <c r="D66" s="5" t="n">
-        <v>4300000</v>
+        <v>3770000</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>0.4424</v>
+        <v>0.7472</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>32.14</v>
+        <v>46.12</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>147.67</v>
+        <v>33.75</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>0.004099999999999999</v>
+        <v>0.0178</v>
       </c>
       <c r="J66" s="4" t="n">
-        <v>-2.9577</v>
+        <v>-0.9085</v>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST ANA</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TEKSTİL DERİ, BIST KATILIM TÜM, BIST ANA, BIST KAYSERİ</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr"/>
@@ -3373,35 +3371,35 @@
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>PSGYO</t>
+          <t>MSGYO</t>
         </is>
       </c>
       <c r="B67" s="7" t="n">
-        <v>3.16</v>
+        <v>6.01</v>
       </c>
       <c r="C67" s="8" t="n">
-        <v>-0.0063</v>
+        <v>-0.005</v>
       </c>
       <c r="D67" s="9" t="n">
-        <v>274580000</v>
+        <v>4300000</v>
       </c>
       <c r="E67" s="8" t="n">
-        <v>0.4281</v>
+        <v>0.4424</v>
       </c>
       <c r="F67" s="7" t="n">
-        <v>53.75</v>
+        <v>32.14</v>
       </c>
       <c r="G67" s="7" t="n">
-        <v>4.25</v>
+        <v>147.67</v>
       </c>
       <c r="H67" s="7" t="n">
-        <v>0.54</v>
+        <v>0.53</v>
       </c>
       <c r="I67" s="8" t="n">
-        <v>0.1378</v>
+        <v>0.004099999999999999</v>
       </c>
       <c r="J67" s="8" t="n">
-        <v>6.6184</v>
+        <v>-2.9577</v>
       </c>
       <c r="K67" s="6" t="inlineStr">
         <is>
@@ -3410,7 +3408,7 @@
       </c>
       <c r="L67" s="6" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU</t>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST ANA</t>
         </is>
       </c>
       <c r="M67" s="6" t="inlineStr"/>
@@ -3418,44 +3416,44 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>SISE</t>
+          <t>PSGYO</t>
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>46.18</v>
+        <v>3.16</v>
       </c>
       <c r="C68" s="4" t="n">
-        <v>0.0061</v>
+        <v>-0.0063</v>
       </c>
       <c r="D68" s="5" t="n">
-        <v>93630000</v>
+        <v>274580000</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>0.4034</v>
+        <v>0.4281</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>44.27</v>
+        <v>53.75</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>12.32</v>
+        <v>4.25</v>
       </c>
       <c r="H68" s="3" t="n">
         <v>0.54</v>
       </c>
       <c r="I68" s="4" t="n">
-        <v>0.044</v>
+        <v>0.1378</v>
       </c>
       <c r="J68" s="4" t="n">
-        <v>-0.5445</v>
+        <v>6.6184</v>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı tüketim malları</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 30, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST HOLDING VE YATIRIM, BIST 50, BIST MALİ, BIST İSTANBUL, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25, STOXX Emerging Markets 1500</t>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr"/>
@@ -3463,42 +3461,44 @@
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>ENTRA</t>
+          <t>SISE</t>
         </is>
       </c>
       <c r="B69" s="7" t="n">
-        <v>10.27</v>
+        <v>46.18</v>
       </c>
       <c r="C69" s="8" t="n">
-        <v>0.0049</v>
+        <v>0.0061</v>
       </c>
       <c r="D69" s="9" t="n">
-        <v>23740000</v>
+        <v>93630000</v>
       </c>
       <c r="E69" s="8" t="n">
-        <v>0.1936</v>
+        <v>0.4034</v>
       </c>
       <c r="F69" s="7" t="n">
-        <v>37.06</v>
-      </c>
-      <c r="G69" s="6" t="inlineStr"/>
+        <v>44.27</v>
+      </c>
+      <c r="G69" s="7" t="n">
+        <v>12.32</v>
+      </c>
       <c r="H69" s="7" t="n">
         <v>0.54</v>
       </c>
       <c r="I69" s="8" t="n">
-        <v>-0.0568</v>
+        <v>0.044</v>
       </c>
       <c r="J69" s="8" t="n">
-        <v>-24.3409</v>
+        <v>-0.5445</v>
       </c>
       <c r="K69" s="6" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Dayanıklı tüketim malları</t>
         </is>
       </c>
       <c r="L69" s="6" t="inlineStr">
         <is>
-          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST YILDIZ, BIST ANKARA</t>
+          <t>BIST 100, BIST 30, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST HOLDING VE YATIRIM, BIST 50, BIST MALİ, BIST İSTANBUL, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25, STOXX Emerging Markets 1500</t>
         </is>
       </c>
       <c r="M69" s="6" t="inlineStr"/>
@@ -3506,42 +3506,42 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>SNICA</t>
+          <t>ENTRA</t>
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>4.29</v>
+        <v>10.27</v>
       </c>
       <c r="C70" s="4" t="n">
-        <v>-0.0381</v>
+        <v>0.0049</v>
       </c>
       <c r="D70" s="5" t="n">
-        <v>20120000</v>
+        <v>23740000</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>0.5366</v>
+        <v>0.1936</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>53.61</v>
+        <v>37.06</v>
       </c>
       <c r="G70" s="2" t="inlineStr"/>
       <c r="H70" s="3" t="n">
         <v>0.54</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>-0.2148</v>
+        <v>-0.0568</v>
       </c>
       <c r="J70" s="4" t="n">
-        <v>-1.5579</v>
+        <v>-24.3409</v>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST KATILIM TÜM, BIST ANA, BIST MANİSA</t>
+          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST YILDIZ, BIST ANKARA</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr"/>
@@ -3549,42 +3549,44 @@
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>ARSAN</t>
+          <t>BESLR</t>
         </is>
       </c>
       <c r="B71" s="7" t="n">
-        <v>3.49</v>
+        <v>15.12</v>
       </c>
       <c r="C71" s="8" t="n">
-        <v>-0.0197</v>
+        <v>-0.0508</v>
       </c>
       <c r="D71" s="9" t="n">
-        <v>44280000</v>
+        <v>7120000</v>
       </c>
       <c r="E71" s="8" t="n">
-        <v>0.4012</v>
+        <v>0.2949</v>
       </c>
       <c r="F71" s="7" t="n">
-        <v>42.63</v>
-      </c>
-      <c r="G71" s="6" t="inlineStr"/>
+        <v>52.36</v>
+      </c>
+      <c r="G71" s="7" t="n">
+        <v>17.73</v>
+      </c>
       <c r="H71" s="7" t="n">
         <v>0.54</v>
       </c>
       <c r="I71" s="8" t="n">
-        <v>-0.047</v>
+        <v>0.0357</v>
       </c>
       <c r="J71" s="8" t="n">
-        <v>0.1821</v>
+        <v>-0.7203000000000001</v>
       </c>
       <c r="K71" s="6" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="L71" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST ANA</t>
+          <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST BURSA</t>
         </is>
       </c>
       <c r="M71" s="6" t="inlineStr"/>
@@ -3592,33 +3594,33 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>SILVR</t>
+          <t>SNICA</t>
         </is>
       </c>
       <c r="B72" s="3" t="n">
-        <v>2.69</v>
+        <v>4.29</v>
       </c>
       <c r="C72" s="4" t="n">
-        <v>-0.0218</v>
+        <v>-0.0381</v>
       </c>
       <c r="D72" s="5" t="n">
-        <v>5040000</v>
+        <v>20120000</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>0.5807</v>
+        <v>0.5366</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>55.37</v>
+        <v>53.61</v>
       </c>
       <c r="G72" s="2" t="inlineStr"/>
       <c r="H72" s="3" t="n">
-        <v>0.55</v>
+        <v>0.54</v>
       </c>
       <c r="I72" s="4" t="n">
-        <v>-0.1455</v>
+        <v>-0.2148</v>
       </c>
       <c r="J72" s="4" t="n">
-        <v>0.4076</v>
+        <v>-1.5579</v>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
@@ -3627,7 +3629,7 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST KATILIM TÜM</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST KATILIM TÜM, BIST ANA, BIST MANİSA</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr"/>
@@ -3635,34 +3637,34 @@
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>BAGFS</t>
+          <t>ARSAN</t>
         </is>
       </c>
       <c r="B73" s="7" t="n">
-        <v>29.86</v>
+        <v>3.49</v>
       </c>
       <c r="C73" s="8" t="n">
-        <v>-0.0368</v>
+        <v>-0.0197</v>
       </c>
       <c r="D73" s="9" t="n">
-        <v>4620000</v>
+        <v>44280000</v>
       </c>
       <c r="E73" s="8" t="n">
-        <v>0.5611</v>
+        <v>0.4012</v>
       </c>
       <c r="F73" s="7" t="n">
-        <v>34.08</v>
-      </c>
-      <c r="G73" s="7" t="n">
-        <v>47.77</v>
-      </c>
+        <v>42.63</v>
+      </c>
+      <c r="G73" s="6" t="inlineStr"/>
       <c r="H73" s="7" t="n">
-        <v>0.55</v>
+        <v>0.54</v>
       </c>
       <c r="I73" s="8" t="n">
-        <v>0.0132</v>
-      </c>
-      <c r="J73" s="6" t="inlineStr"/>
+        <v>-0.047</v>
+      </c>
+      <c r="J73" s="8" t="n">
+        <v>0.1821</v>
+      </c>
       <c r="K73" s="6" t="inlineStr">
         <is>
           <t>İşlenebilen endüstriler</t>
@@ -3670,7 +3672,7 @@
       </c>
       <c r="L73" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST BALIKESİR</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST ANA</t>
         </is>
       </c>
       <c r="M73" s="6" t="inlineStr"/>
@@ -3678,42 +3680,42 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>AVPGY</t>
+          <t>SILVR</t>
         </is>
       </c>
       <c r="B74" s="3" t="n">
-        <v>62.15</v>
+        <v>2.69</v>
       </c>
       <c r="C74" s="4" t="n">
-        <v>-0.0475</v>
+        <v>-0.0218</v>
       </c>
       <c r="D74" s="5" t="n">
-        <v>1210000</v>
+        <v>5040000</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>0.2632</v>
+        <v>0.5807</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>54.15</v>
-      </c>
-      <c r="G74" s="3" t="n">
-        <v>12.61</v>
-      </c>
+        <v>55.37</v>
+      </c>
+      <c r="G74" s="2" t="inlineStr"/>
       <c r="H74" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="I74" s="4" t="n">
-        <v>0.0496</v>
-      </c>
-      <c r="J74" s="2" t="inlineStr"/>
+        <v>-0.1455</v>
+      </c>
+      <c r="J74" s="4" t="n">
+        <v>0.4076</v>
+      </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST KATILIM TÜM, BIST YILDIZ</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST KATILIM TÜM</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr"/>
@@ -3721,42 +3723,42 @@
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>AYEN</t>
+          <t>AVPGY</t>
         </is>
       </c>
       <c r="B75" s="7" t="n">
-        <v>34.76</v>
+        <v>62.15</v>
       </c>
       <c r="C75" s="8" t="n">
-        <v>0.0389</v>
+        <v>-0.0475</v>
       </c>
       <c r="D75" s="9" t="n">
-        <v>2570000</v>
+        <v>1210000</v>
       </c>
       <c r="E75" s="8" t="n">
-        <v>0.1697</v>
+        <v>0.2632</v>
       </c>
       <c r="F75" s="7" t="n">
-        <v>51.68</v>
+        <v>54.15</v>
       </c>
       <c r="G75" s="7" t="n">
-        <v>44.89</v>
+        <v>12.61</v>
       </c>
       <c r="H75" s="7" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="I75" s="8" t="n">
-        <v>0.0143</v>
+        <v>0.0496</v>
       </c>
       <c r="J75" s="6" t="inlineStr"/>
       <c r="K75" s="6" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L75" s="6" t="inlineStr">
         <is>
-          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST KATILIM TÜM, BIST ANA, BIST TEMETTU, BIST KAYSERİ, BIST KATILIM TEMETTU</t>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST KATILIM TÜM, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M75" s="6" t="inlineStr"/>
@@ -3764,42 +3766,42 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>PRKME</t>
+          <t>AYEN</t>
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>17.78</v>
+        <v>34.76</v>
       </c>
       <c r="C76" s="4" t="n">
-        <v>-0.0258</v>
+        <v>0.0389</v>
       </c>
       <c r="D76" s="5" t="n">
-        <v>3790000</v>
+        <v>2570000</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>0.32</v>
+        <v>0.1697</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>37.99</v>
-      </c>
-      <c r="G76" s="2" t="inlineStr"/>
+        <v>51.68</v>
+      </c>
+      <c r="G76" s="3" t="n">
+        <v>44.89</v>
+      </c>
       <c r="H76" s="3" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="I76" s="4" t="n">
-        <v>-0.0541</v>
-      </c>
-      <c r="J76" s="4" t="n">
-        <v>-9.4055</v>
-      </c>
+        <v>0.0143</v>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST MADENCİLİK, BIST KATILIM TÜM, BIST ANA, BIST KURUMSAL YÖNETİM</t>
+          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST KATILIM TÜM, BIST ANA, BIST TEMETTU, BIST KAYSERİ, BIST KATILIM TEMETTU</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr"/>
@@ -3807,33 +3809,33 @@
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>KOCMT</t>
+          <t>PRKME</t>
         </is>
       </c>
       <c r="B77" s="7" t="n">
-        <v>2.66</v>
+        <v>17.78</v>
       </c>
       <c r="C77" s="8" t="n">
-        <v>0.027</v>
+        <v>-0.0258</v>
       </c>
       <c r="D77" s="9" t="n">
-        <v>39990000</v>
+        <v>3790000</v>
       </c>
       <c r="E77" s="8" t="n">
-        <v>0.2582</v>
+        <v>0.32</v>
       </c>
       <c r="F77" s="7" t="n">
-        <v>52.78</v>
+        <v>37.99</v>
       </c>
       <c r="G77" s="6" t="inlineStr"/>
       <c r="H77" s="7" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="I77" s="8" t="n">
-        <v>-0.0862</v>
+        <v>-0.0541</v>
       </c>
       <c r="J77" s="8" t="n">
-        <v>-114.5083</v>
+        <v>-9.4055</v>
       </c>
       <c r="K77" s="6" t="inlineStr">
         <is>
@@ -3842,7 +3844,7 @@
       </c>
       <c r="L77" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST HALKA ARZ, BIST KATILIM TÜM, BIST YILDIZ</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST MADENCİLİK, BIST KATILIM TÜM, BIST ANA, BIST KURUMSAL YÖNETİM</t>
         </is>
       </c>
       <c r="M77" s="6" t="inlineStr"/>
@@ -3850,42 +3852,42 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>ALARK</t>
+          <t>KOCMT</t>
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>95.45</v>
+        <v>2.66</v>
       </c>
       <c r="C78" s="4" t="n">
-        <v>0.028</v>
+        <v>0.027</v>
       </c>
       <c r="D78" s="5" t="n">
-        <v>5810000</v>
+        <v>39990000</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>0.2929</v>
+        <v>0.2582</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>48.66</v>
+        <v>52.78</v>
       </c>
       <c r="G78" s="2" t="inlineStr"/>
       <c r="H78" s="3" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="I78" s="4" t="n">
-        <v>-0.0125</v>
+        <v>-0.0862</v>
       </c>
       <c r="J78" s="4" t="n">
-        <v>-1.2814</v>
+        <v>-114.5083</v>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST HOLDING VE YATIRIM, BIST 50, BIST MALİ, BIST İSTANBUL, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU 25, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST 50-30, BIST 50-30 AGIRLIK SINIRLAMALI 25, BIST 50-30 AĞIRLIK SINIRLAMALI 10</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST HALKA ARZ, BIST KATILIM TÜM, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr"/>
@@ -3893,33 +3895,33 @@
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>SEGYO</t>
+          <t>ALARK</t>
         </is>
       </c>
       <c r="B79" s="7" t="n">
-        <v>4.67</v>
+        <v>95.45</v>
       </c>
       <c r="C79" s="8" t="n">
-        <v>-0.0127</v>
-      </c>
-      <c r="D79" s="7" t="n">
-        <v>16100000</v>
+        <v>0.028</v>
+      </c>
+      <c r="D79" s="9" t="n">
+        <v>5810000</v>
       </c>
       <c r="E79" s="8" t="n">
-        <v>0.2445</v>
+        <v>0.2929</v>
       </c>
       <c r="F79" s="7" t="n">
-        <v>43.32</v>
+        <v>48.66</v>
       </c>
       <c r="G79" s="6" t="inlineStr"/>
       <c r="H79" s="7" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="I79" s="8" t="n">
-        <v>-0.2247</v>
+        <v>-0.0125</v>
       </c>
       <c r="J79" s="8" t="n">
-        <v>0.5464</v>
+        <v>-1.2814</v>
       </c>
       <c r="K79" s="6" t="inlineStr">
         <is>
@@ -3928,7 +3930,7 @@
       </c>
       <c r="L79" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST ANA</t>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST HOLDING VE YATIRIM, BIST 50, BIST MALİ, BIST İSTANBUL, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU 25, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST 50-30, BIST 50-30 AGIRLIK SINIRLAMALI 25, BIST 50-30 AĞIRLIK SINIRLAMALI 10</t>
         </is>
       </c>
       <c r="M79" s="6" t="inlineStr"/>
@@ -3936,38 +3938,42 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>TUKAS</t>
+          <t>SEGYO</t>
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>2.42</v>
+        <v>4.67</v>
       </c>
       <c r="C80" s="4" t="n">
-        <v>-0.032</v>
-      </c>
-      <c r="D80" s="5" t="n">
-        <v>216810000</v>
+        <v>-0.0127</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>16100000</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>0.5413</v>
+        <v>0.2445</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>42.04</v>
+        <v>43.32</v>
       </c>
       <c r="G80" s="2" t="inlineStr"/>
       <c r="H80" s="3" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="2" t="inlineStr"/>
+      <c r="I80" s="4" t="n">
+        <v>-0.2247</v>
+      </c>
+      <c r="J80" s="4" t="n">
+        <v>0.5464</v>
+      </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST GIDA ICECEK, BIST SINAI, BIST TÜM, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST İZMİR, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST ANA</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr"/>
@@ -3975,42 +3981,38 @@
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>TSPOR</t>
+          <t>TUKAS</t>
         </is>
       </c>
       <c r="B81" s="7" t="n">
-        <v>0.99</v>
+        <v>2.42</v>
       </c>
       <c r="C81" s="8" t="n">
-        <v>0</v>
+        <v>-0.032</v>
       </c>
       <c r="D81" s="9" t="n">
-        <v>343870000</v>
+        <v>216810000</v>
       </c>
       <c r="E81" s="8" t="n">
-        <v>0.49</v>
+        <v>0.5413</v>
       </c>
       <c r="F81" s="7" t="n">
-        <v>47.34</v>
+        <v>42.04</v>
       </c>
       <c r="G81" s="6" t="inlineStr"/>
       <c r="H81" s="7" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="I81" s="8" t="n">
-        <v>-0.1002</v>
-      </c>
-      <c r="J81" s="8" t="n">
-        <v>-2.0054</v>
-      </c>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="I81" s="6" t="inlineStr"/>
+      <c r="J81" s="6" t="inlineStr"/>
       <c r="K81" s="6" t="inlineStr">
         <is>
-          <t>Tüketici hizmetleri</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="L81" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST SPOR, BIST HİZMETLER, BIST YILDIZ</t>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST GIDA ICECEK, BIST SINAI, BIST TÜM, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST İZMİR, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
         </is>
       </c>
       <c r="M81" s="6" t="inlineStr"/>
@@ -4018,42 +4020,42 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>IZMDC</t>
+          <t>TSPOR</t>
         </is>
       </c>
       <c r="B82" s="3" t="n">
-        <v>7.33</v>
+        <v>0.99</v>
       </c>
       <c r="C82" s="4" t="n">
-        <v>-0.0291</v>
+        <v>0</v>
       </c>
       <c r="D82" s="5" t="n">
-        <v>18450000</v>
+        <v>343870000</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>0.4187</v>
+        <v>0.49</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>48.66</v>
+        <v>47.34</v>
       </c>
       <c r="G82" s="2" t="inlineStr"/>
       <c r="H82" s="3" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="I82" s="4" t="n">
-        <v>-0.0983</v>
+        <v>-0.1002</v>
       </c>
       <c r="J82" s="4" t="n">
-        <v>0.5235</v>
+        <v>-2.0054</v>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Tüketici hizmetleri</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST ANA, BIST İZMİR</t>
+          <t>BIST TUM-100, BIST TÜM, BIST SPOR, BIST HİZMETLER, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr"/>
@@ -4061,42 +4063,42 @@
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>USAK</t>
+          <t>IZMDC</t>
         </is>
       </c>
       <c r="B83" s="7" t="n">
-        <v>1.59</v>
+        <v>7.33</v>
       </c>
       <c r="C83" s="8" t="n">
-        <v>-0.0245</v>
+        <v>-0.0291</v>
       </c>
       <c r="D83" s="9" t="n">
-        <v>103680000</v>
+        <v>18450000</v>
       </c>
       <c r="E83" s="8" t="n">
-        <v>0.8108</v>
+        <v>0.4187</v>
       </c>
       <c r="F83" s="7" t="n">
-        <v>35.38</v>
-      </c>
-      <c r="G83" s="7" t="n">
-        <v>31.18</v>
-      </c>
+        <v>48.66</v>
+      </c>
+      <c r="G83" s="6" t="inlineStr"/>
       <c r="H83" s="7" t="n">
         <v>0.58</v>
       </c>
       <c r="I83" s="8" t="n">
-        <v>0.0222</v>
-      </c>
-      <c r="J83" s="6" t="inlineStr"/>
+        <v>-0.0983</v>
+      </c>
+      <c r="J83" s="8" t="n">
+        <v>0.5235</v>
+      </c>
       <c r="K83" s="6" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="L83" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST KATILIM 50</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST ANA, BIST İZMİR</t>
         </is>
       </c>
       <c r="M83" s="6" t="inlineStr"/>
@@ -4104,40 +4106,42 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>OSTIM</t>
+          <t>USAK</t>
         </is>
       </c>
       <c r="B84" s="3" t="n">
-        <v>2.69</v>
+        <v>1.59</v>
       </c>
       <c r="C84" s="4" t="n">
-        <v>-0.011</v>
+        <v>-0.0245</v>
       </c>
       <c r="D84" s="5" t="n">
-        <v>18250000</v>
-      </c>
-      <c r="E84" s="2" t="inlineStr"/>
+        <v>103680000</v>
+      </c>
+      <c r="E84" s="4" t="n">
+        <v>0.8108</v>
+      </c>
       <c r="F84" s="3" t="n">
-        <v>36.86</v>
+        <v>35.38</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>150.28</v>
+        <v>31.18</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="I84" s="4" t="n">
-        <v>0.004500000000000001</v>
+        <v>0.0222</v>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>Çeşitli Hizmetler</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST KATILIM TÜM, BIST ANA, BIST ANKARA</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST KATILIM 50</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr"/>
@@ -4145,42 +4149,40 @@
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>TEKTU</t>
+          <t>OSTIM</t>
         </is>
       </c>
       <c r="B85" s="7" t="n">
-        <v>10.6</v>
+        <v>2.69</v>
       </c>
       <c r="C85" s="8" t="n">
-        <v>-0.0028</v>
+        <v>-0.011</v>
       </c>
       <c r="D85" s="9" t="n">
-        <v>15440000</v>
-      </c>
-      <c r="E85" s="8" t="n">
-        <v>0.6518</v>
-      </c>
+        <v>18250000</v>
+      </c>
+      <c r="E85" s="6" t="inlineStr"/>
       <c r="F85" s="7" t="n">
-        <v>42.17</v>
-      </c>
-      <c r="G85" s="6" t="inlineStr"/>
+        <v>36.86</v>
+      </c>
+      <c r="G85" s="7" t="n">
+        <v>150.28</v>
+      </c>
       <c r="H85" s="7" t="n">
         <v>0.59</v>
       </c>
       <c r="I85" s="8" t="n">
-        <v>-0.1339</v>
-      </c>
-      <c r="J85" s="8" t="n">
-        <v>-19.7854</v>
-      </c>
+        <v>0.004500000000000001</v>
+      </c>
+      <c r="J85" s="6" t="inlineStr"/>
       <c r="K85" s="6" t="inlineStr">
         <is>
-          <t>Tüketici hizmetleri</t>
+          <t>Çeşitli Hizmetler</t>
         </is>
       </c>
       <c r="L85" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TURİZM, BIST HİZMETLER, BIST ANA, BIST ANTALYA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST KATILIM TÜM, BIST ANA, BIST ANKARA</t>
         </is>
       </c>
       <c r="M85" s="6" t="inlineStr"/>
@@ -4188,42 +4190,42 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>ESEN</t>
+          <t>TEKTU</t>
         </is>
       </c>
       <c r="B86" s="3" t="n">
-        <v>3.91</v>
+        <v>10.6</v>
       </c>
       <c r="C86" s="4" t="n">
-        <v>-0.0076</v>
+        <v>-0.0028</v>
       </c>
       <c r="D86" s="5" t="n">
-        <v>134260000</v>
+        <v>15440000</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>0.3749</v>
+        <v>0.6518</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>48.31</v>
-      </c>
-      <c r="G86" s="3" t="n">
-        <v>8.58</v>
-      </c>
+        <v>42.17</v>
+      </c>
+      <c r="G86" s="2" t="inlineStr"/>
       <c r="H86" s="3" t="n">
         <v>0.59</v>
       </c>
       <c r="I86" s="4" t="n">
-        <v>0.0048</v>
-      </c>
-      <c r="J86" s="2" t="inlineStr"/>
+        <v>-0.1339</v>
+      </c>
+      <c r="J86" s="4" t="n">
+        <v>-19.7854</v>
+      </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Tüketici hizmetleri</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST ANKARA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TURİZM, BIST HİZMETLER, BIST ANA, BIST ANTALYA</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr"/>
@@ -4231,42 +4233,42 @@
     <row r="87">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>DOAS</t>
+          <t>ESEN</t>
         </is>
       </c>
       <c r="B87" s="7" t="n">
-        <v>184.3</v>
+        <v>3.91</v>
       </c>
       <c r="C87" s="8" t="n">
-        <v>0.0354</v>
+        <v>-0.0076</v>
       </c>
       <c r="D87" s="9" t="n">
-        <v>1610000</v>
+        <v>134260000</v>
       </c>
       <c r="E87" s="8" t="n">
-        <v>0.395</v>
+        <v>0.3749</v>
       </c>
       <c r="F87" s="7" t="n">
-        <v>47.43</v>
+        <v>48.31</v>
       </c>
       <c r="G87" s="7" t="n">
-        <v>13.99</v>
+        <v>8.58</v>
       </c>
       <c r="H87" s="7" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="I87" s="8" t="n">
-        <v>0.0472</v>
+        <v>0.0048</v>
       </c>
       <c r="J87" s="6" t="inlineStr"/>
       <c r="K87" s="6" t="inlineStr">
         <is>
-          <t>Perakende satış</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="L87" s="6" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST 50, BIST TİCARET, BIST HİZMETLER, BIST İSTANBUL, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU 25, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST 50-30, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST 50-30 AGIRLIK SINIRLAMALI 25, BIST 50-30 AĞIRLIK SINIRLAMALI 10</t>
+          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST ANKARA</t>
         </is>
       </c>
       <c r="M87" s="6" t="inlineStr"/>
@@ -4274,44 +4276,42 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>MHRGY</t>
+          <t>DOAS</t>
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>4.42</v>
+        <v>184.3</v>
       </c>
       <c r="C88" s="4" t="n">
-        <v>-0.0178</v>
+        <v>0.0354</v>
       </c>
       <c r="D88" s="5" t="n">
-        <v>11220000</v>
+        <v>1610000</v>
       </c>
       <c r="E88" s="4" t="n">
-        <v>0.2243</v>
+        <v>0.395</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>68.81</v>
+        <v>47.43</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>12.24</v>
+        <v>13.99</v>
       </c>
       <c r="H88" s="3" t="n">
         <v>0.6</v>
       </c>
       <c r="I88" s="4" t="n">
-        <v>0.0565</v>
-      </c>
-      <c r="J88" s="4" t="n">
-        <v>-1.1809</v>
-      </c>
+        <v>0.0472</v>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Perakende satış</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST ANA, BIST KURUMSAL YÖNETİM</t>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST 50, BIST TİCARET, BIST HİZMETLER, BIST İSTANBUL, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU 25, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST 50-30, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST 50-30 AGIRLIK SINIRLAMALI 25, BIST 50-30 AĞIRLIK SINIRLAMALI 10</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr"/>
@@ -4319,44 +4319,44 @@
     <row r="89">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>GOLTS</t>
+          <t>MHRGY</t>
         </is>
       </c>
       <c r="B89" s="7" t="n">
-        <v>351.25</v>
+        <v>4.42</v>
       </c>
       <c r="C89" s="8" t="n">
-        <v>-0.0216</v>
+        <v>-0.0178</v>
       </c>
       <c r="D89" s="9" t="n">
-        <v>165030</v>
+        <v>11220000</v>
       </c>
       <c r="E89" s="8" t="n">
-        <v>0.5911999999999999</v>
+        <v>0.2243</v>
       </c>
       <c r="F89" s="7" t="n">
-        <v>36.49</v>
+        <v>68.81</v>
       </c>
       <c r="G89" s="7" t="n">
-        <v>16.65</v>
+        <v>12.24</v>
       </c>
       <c r="H89" s="7" t="n">
         <v>0.6</v>
       </c>
       <c r="I89" s="8" t="n">
-        <v>0.0401</v>
+        <v>0.0565</v>
       </c>
       <c r="J89" s="8" t="n">
-        <v>-0.9365000000000001</v>
+        <v>-1.1809</v>
       </c>
       <c r="K89" s="6" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L89" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST KATILIM TÜM, BIST YILDIZ, BIST TEMETTU, BIST KATILIM TEMETTU</t>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST ANA, BIST KURUMSAL YÖNETİM</t>
         </is>
       </c>
       <c r="M89" s="6" t="inlineStr"/>
@@ -4364,44 +4364,44 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>BESLR</t>
+          <t>GOLTS</t>
         </is>
       </c>
       <c r="B90" s="3" t="n">
-        <v>15.12</v>
+        <v>351.25</v>
       </c>
       <c r="C90" s="4" t="n">
-        <v>-0.0508</v>
+        <v>-0.0216</v>
       </c>
       <c r="D90" s="5" t="n">
-        <v>7120000</v>
+        <v>165030</v>
       </c>
       <c r="E90" s="4" t="n">
-        <v>0.2949</v>
+        <v>0.5911999999999999</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>52.36</v>
+        <v>36.49</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>18.94</v>
+        <v>16.65</v>
       </c>
       <c r="H90" s="3" t="n">
         <v>0.6</v>
       </c>
       <c r="I90" s="4" t="n">
-        <v>0.0371</v>
+        <v>0.0401</v>
       </c>
       <c r="J90" s="4" t="n">
-        <v>2.5571</v>
+        <v>-0.9365000000000001</v>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST BURSA</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST KATILIM TÜM, BIST YILDIZ, BIST TEMETTU, BIST KATILIM TEMETTU</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr"/>
@@ -4409,44 +4409,40 @@
     <row r="91">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>RYGYO</t>
+          <t>AKENR</t>
         </is>
       </c>
       <c r="B91" s="7" t="n">
-        <v>29.08</v>
+        <v>11.95</v>
       </c>
       <c r="C91" s="8" t="n">
-        <v>-0.0129</v>
+        <v>-0.0508</v>
       </c>
       <c r="D91" s="9" t="n">
-        <v>1650000</v>
+        <v>42540000</v>
       </c>
       <c r="E91" s="8" t="n">
-        <v>0.2915</v>
+        <v>0.2528</v>
       </c>
       <c r="F91" s="7" t="n">
-        <v>36.98</v>
-      </c>
-      <c r="G91" s="7" t="n">
-        <v>3.38</v>
-      </c>
+        <v>54.71</v>
+      </c>
+      <c r="G91" s="6" t="inlineStr"/>
       <c r="H91" s="7" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="I91" s="8" t="n">
-        <v>0.2239</v>
-      </c>
-      <c r="J91" s="8" t="n">
-        <v>-0.9611</v>
-      </c>
+        <v>-0.3405</v>
+      </c>
+      <c r="J91" s="6" t="inlineStr"/>
       <c r="K91" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="L91" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST YILDIZ</t>
+          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM</t>
         </is>
       </c>
       <c r="M91" s="6" t="inlineStr"/>
@@ -4454,42 +4450,44 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>PENGD</t>
+          <t>RYGYO</t>
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>14.88</v>
+        <v>29.08</v>
       </c>
       <c r="C92" s="4" t="n">
-        <v>0.008800000000000001</v>
+        <v>-0.0129</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>14400000</v>
+        <v>1650000</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>0.7673000000000001</v>
+        <v>0.2915</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>65.33</v>
-      </c>
-      <c r="G92" s="2" t="inlineStr"/>
+        <v>36.98</v>
+      </c>
+      <c r="G92" s="3" t="n">
+        <v>3.38</v>
+      </c>
       <c r="H92" s="3" t="n">
         <v>0.61</v>
       </c>
       <c r="I92" s="4" t="n">
-        <v>-0.059</v>
+        <v>0.2239</v>
       </c>
       <c r="J92" s="4" t="n">
-        <v>-2.8382</v>
+        <v>-0.9611</v>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST KATILIM TÜM, BIST ANA, BIST BURSA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr"/>
@@ -4497,42 +4495,42 @@
     <row r="93">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>BEGYO</t>
+          <t>PENGD</t>
         </is>
       </c>
       <c r="B93" s="7" t="n">
-        <v>4.18</v>
+        <v>14.88</v>
       </c>
       <c r="C93" s="8" t="n">
-        <v>-0.0279</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="D93" s="9" t="n">
-        <v>15940000</v>
+        <v>14400000</v>
       </c>
       <c r="E93" s="8" t="n">
-        <v>0.3558</v>
+        <v>0.7673000000000001</v>
       </c>
       <c r="F93" s="7" t="n">
-        <v>41.37</v>
+        <v>65.33</v>
       </c>
       <c r="G93" s="6" t="inlineStr"/>
       <c r="H93" s="7" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="I93" s="8" t="n">
-        <v>-0.0645</v>
+        <v>-0.059</v>
       </c>
       <c r="J93" s="8" t="n">
-        <v>-2.8806</v>
+        <v>-2.8382</v>
       </c>
       <c r="K93" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="L93" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST KATILIM TÜM, BIST ANA, BIST BURSA</t>
         </is>
       </c>
       <c r="M93" s="6" t="inlineStr"/>
@@ -4540,35 +4538,33 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>PRDGS</t>
+          <t>BEGYO</t>
         </is>
       </c>
       <c r="B94" s="3" t="n">
-        <v>7.76</v>
+        <v>4.18</v>
       </c>
       <c r="C94" s="4" t="n">
-        <v>0.0117</v>
+        <v>-0.0279</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>9570000</v>
+        <v>15940000</v>
       </c>
       <c r="E94" s="4" t="n">
-        <v>0.5656</v>
+        <v>0.3558</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>45.76</v>
-      </c>
-      <c r="G94" s="3" t="n">
-        <v>155.51</v>
-      </c>
+        <v>41.37</v>
+      </c>
+      <c r="G94" s="2" t="inlineStr"/>
       <c r="H94" s="3" t="n">
         <v>0.62</v>
       </c>
       <c r="I94" s="4" t="n">
-        <v>0.0046</v>
+        <v>-0.0645</v>
       </c>
       <c r="J94" s="4" t="n">
-        <v>-1.5958</v>
+        <v>-2.8806</v>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
@@ -4577,7 +4573,7 @@
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST MALİ, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr"/>
@@ -4585,35 +4581,35 @@
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>TSGYO</t>
+          <t>PRDGS</t>
         </is>
       </c>
       <c r="B95" s="7" t="n">
-        <v>6.56</v>
+        <v>7.76</v>
       </c>
       <c r="C95" s="8" t="n">
-        <v>0.0015</v>
+        <v>0.0117</v>
       </c>
       <c r="D95" s="9" t="n">
-        <v>2100000</v>
+        <v>9570000</v>
       </c>
       <c r="E95" s="8" t="n">
-        <v>0.1139</v>
+        <v>0.5656</v>
       </c>
       <c r="F95" s="7" t="n">
-        <v>38.95</v>
+        <v>45.76</v>
       </c>
       <c r="G95" s="7" t="n">
-        <v>5466.67</v>
+        <v>155.51</v>
       </c>
       <c r="H95" s="7" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="I95" s="8" t="n">
-        <v>0.0001</v>
+        <v>0.0046</v>
       </c>
       <c r="J95" s="8" t="n">
-        <v>-2.3242</v>
+        <v>-1.5958</v>
       </c>
       <c r="K95" s="6" t="inlineStr">
         <is>
@@ -4622,7 +4618,7 @@
       </c>
       <c r="L95" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST MALİ, BIST ANA</t>
         </is>
       </c>
       <c r="M95" s="6" t="inlineStr"/>
@@ -4630,44 +4626,44 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>A1YEN</t>
+          <t>TSGYO</t>
         </is>
       </c>
       <c r="B96" s="3" t="n">
-        <v>3.43</v>
+        <v>6.56</v>
       </c>
       <c r="C96" s="4" t="n">
-        <v>-0.0311</v>
+        <v>0.0015</v>
       </c>
       <c r="D96" s="5" t="n">
-        <v>103270000</v>
+        <v>2100000</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>0.8</v>
+        <v>0.1139</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>48.72</v>
+        <v>38.95</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>26.84</v>
+        <v>5466.67</v>
       </c>
       <c r="H96" s="3" t="n">
         <v>0.63</v>
       </c>
       <c r="I96" s="4" t="n">
-        <v>0.0265</v>
+        <v>0.0001</v>
       </c>
       <c r="J96" s="4" t="n">
-        <v>-0.2732</v>
+        <v>-2.3242</v>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST ANA, BIST MANİSA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST ANA</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr"/>
@@ -4675,40 +4671,44 @@
     <row r="97">
       <c r="A97" s="6" t="inlineStr">
         <is>
-          <t>BIENY</t>
+          <t>A1YEN</t>
         </is>
       </c>
       <c r="B97" s="7" t="n">
-        <v>23.02</v>
+        <v>3.43</v>
       </c>
       <c r="C97" s="8" t="n">
-        <v>-0.0196</v>
+        <v>-0.0311</v>
       </c>
       <c r="D97" s="9" t="n">
-        <v>3410000</v>
+        <v>103270000</v>
       </c>
       <c r="E97" s="8" t="n">
-        <v>0.2003</v>
+        <v>0.8</v>
       </c>
       <c r="F97" s="7" t="n">
-        <v>39.85</v>
-      </c>
-      <c r="G97" s="6" t="inlineStr"/>
+        <v>48.72</v>
+      </c>
+      <c r="G97" s="7" t="n">
+        <v>26.84</v>
+      </c>
       <c r="H97" s="7" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="I97" s="8" t="n">
-        <v>-0.1204</v>
-      </c>
-      <c r="J97" s="6" t="inlineStr"/>
+        <v>0.0265</v>
+      </c>
+      <c r="J97" s="8" t="n">
+        <v>-0.2732</v>
+      </c>
       <c r="K97" s="6" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="L97" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ</t>
+          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST ANA, BIST MANİSA</t>
         </is>
       </c>
       <c r="M97" s="6" t="inlineStr"/>
@@ -4716,42 +4716,40 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>AVTUR</t>
+          <t>BIENY</t>
         </is>
       </c>
       <c r="B98" s="3" t="n">
-        <v>16.9</v>
+        <v>23.02</v>
       </c>
       <c r="C98" s="4" t="n">
-        <v>0.0305</v>
+        <v>-0.0196</v>
       </c>
       <c r="D98" s="5" t="n">
-        <v>526490</v>
+        <v>3410000</v>
       </c>
       <c r="E98" s="4" t="n">
-        <v>0.3008</v>
+        <v>0.2003</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>34.68</v>
-      </c>
-      <c r="G98" s="3" t="n">
-        <v>12.58</v>
-      </c>
+        <v>39.85</v>
+      </c>
+      <c r="G98" s="2" t="inlineStr"/>
       <c r="H98" s="3" t="n">
         <v>0.64</v>
       </c>
       <c r="I98" s="4" t="n">
-        <v>0.0592</v>
+        <v>-0.1204</v>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>Çeşitli Hizmetler</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TURİZM, BIST HİZMETLER, BIST İSTANBUL</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr"/>
@@ -4759,44 +4757,42 @@
     <row r="99">
       <c r="A99" s="6" t="inlineStr">
         <is>
-          <t>ODAS</t>
+          <t>AVTUR</t>
         </is>
       </c>
       <c r="B99" s="7" t="n">
-        <v>7.19</v>
+        <v>16.9</v>
       </c>
       <c r="C99" s="8" t="n">
-        <v>-0.005500000000000001</v>
+        <v>0.0305</v>
       </c>
       <c r="D99" s="9" t="n">
-        <v>117900000</v>
+        <v>526490</v>
       </c>
       <c r="E99" s="8" t="n">
-        <v>0.7543000000000001</v>
+        <v>0.3008</v>
       </c>
       <c r="F99" s="7" t="n">
-        <v>49.02</v>
+        <v>34.68</v>
       </c>
       <c r="G99" s="7" t="n">
-        <v>39.18</v>
+        <v>12.58</v>
       </c>
       <c r="H99" s="7" t="n">
         <v>0.64</v>
       </c>
       <c r="I99" s="8" t="n">
-        <v>0.0163</v>
-      </c>
-      <c r="J99" s="8" t="n">
-        <v>-1.9379</v>
-      </c>
+        <v>0.0592</v>
+      </c>
+      <c r="J99" s="6" t="inlineStr"/>
       <c r="K99" s="6" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Çeşitli Hizmetler</t>
         </is>
       </c>
       <c r="L99" s="6" t="inlineStr">
         <is>
-          <t>BIST 100, BIST ELEKTRIK, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST HİZMETLER, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KURUMSAL YÖNETİM</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TURİZM, BIST HİZMETLER, BIST İSTANBUL</t>
         </is>
       </c>
       <c r="M99" s="6" t="inlineStr"/>
@@ -4804,44 +4800,44 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>PAGYO</t>
+          <t>ODAS</t>
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>126</v>
+        <v>7.19</v>
       </c>
       <c r="C100" s="4" t="n">
-        <v>-0.0179</v>
+        <v>-0.005500000000000001</v>
       </c>
       <c r="D100" s="5" t="n">
-        <v>452460</v>
+        <v>117900000</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>0.6475</v>
+        <v>0.7543000000000001</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>49.34</v>
+        <v>49.02</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>6.59</v>
+        <v>39.18</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="I100" s="4" t="n">
-        <v>0.1156</v>
+        <v>0.0163</v>
       </c>
       <c r="J100" s="4" t="n">
-        <v>-0.8338</v>
+        <v>-1.9379</v>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST KATILIM TÜM, BIST YILDIZ, BIST TEMETTU, BIST KATILIM TEMETTU</t>
+          <t>BIST 100, BIST ELEKTRIK, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST HİZMETLER, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KURUMSAL YÖNETİM</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr"/>
@@ -4849,44 +4845,44 @@
     <row r="101">
       <c r="A101" s="6" t="inlineStr">
         <is>
-          <t>MEPET</t>
+          <t>PAGYO</t>
         </is>
       </c>
       <c r="B101" s="7" t="n">
-        <v>23.42</v>
+        <v>126</v>
       </c>
       <c r="C101" s="8" t="n">
-        <v>0.0483</v>
+        <v>-0.0179</v>
       </c>
       <c r="D101" s="9" t="n">
-        <v>577310</v>
+        <v>452460</v>
       </c>
       <c r="E101" s="8" t="n">
-        <v>0.9698</v>
+        <v>0.6475</v>
       </c>
       <c r="F101" s="7" t="n">
-        <v>51.62</v>
+        <v>49.34</v>
       </c>
       <c r="G101" s="7" t="n">
-        <v>9.949999999999999</v>
+        <v>6.59</v>
       </c>
       <c r="H101" s="7" t="n">
         <v>0.65</v>
       </c>
       <c r="I101" s="8" t="n">
-        <v>0.0793</v>
+        <v>0.1156</v>
       </c>
       <c r="J101" s="8" t="n">
-        <v>11.6409</v>
+        <v>-0.8338</v>
       </c>
       <c r="K101" s="6" t="inlineStr">
         <is>
-          <t>Perakende satış</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L101" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER</t>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST KATILIM TÜM, BIST YILDIZ, BIST TEMETTU, BIST KATILIM TEMETTU</t>
         </is>
       </c>
       <c r="M101" s="6" t="inlineStr"/>
@@ -4894,42 +4890,44 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>KLMSN</t>
+          <t>MEPET</t>
         </is>
       </c>
       <c r="B102" s="3" t="n">
-        <v>32.5</v>
+        <v>23.42</v>
       </c>
       <c r="C102" s="4" t="n">
-        <v>0.0031</v>
+        <v>0.0483</v>
       </c>
       <c r="D102" s="5" t="n">
-        <v>1500000</v>
+        <v>577310</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>0.3899</v>
+        <v>0.9698</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>41.85</v>
-      </c>
-      <c r="G102" s="2" t="inlineStr"/>
+        <v>51.62</v>
+      </c>
+      <c r="G102" s="3" t="n">
+        <v>9.949999999999999</v>
+      </c>
       <c r="H102" s="3" t="n">
         <v>0.65</v>
       </c>
       <c r="I102" s="4" t="n">
-        <v>-0.1402</v>
+        <v>0.0793</v>
       </c>
       <c r="J102" s="4" t="n">
-        <v>-1.5387</v>
+        <v>11.6409</v>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Perakende satış</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST ANA, BIST MANİSA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr"/>
@@ -4937,40 +4935,42 @@
     <row r="103">
       <c r="A103" s="6" t="inlineStr">
         <is>
-          <t>AVGYO</t>
+          <t>KLMSN</t>
         </is>
       </c>
       <c r="B103" s="7" t="n">
-        <v>12.13</v>
+        <v>32.5</v>
       </c>
       <c r="C103" s="8" t="n">
-        <v>-0.0358</v>
+        <v>0.0031</v>
       </c>
       <c r="D103" s="9" t="n">
-        <v>1600000</v>
+        <v>1500000</v>
       </c>
       <c r="E103" s="8" t="n">
-        <v>0.7618</v>
+        <v>0.3899</v>
       </c>
       <c r="F103" s="7" t="n">
-        <v>43.18</v>
+        <v>41.85</v>
       </c>
       <c r="G103" s="6" t="inlineStr"/>
       <c r="H103" s="7" t="n">
         <v>0.65</v>
       </c>
       <c r="I103" s="8" t="n">
-        <v>-0.0146</v>
-      </c>
-      <c r="J103" s="6" t="inlineStr"/>
+        <v>-0.1402</v>
+      </c>
+      <c r="J103" s="8" t="n">
+        <v>-1.5387</v>
+      </c>
       <c r="K103" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="L103" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST ANA</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST ANA, BIST MANİSA</t>
         </is>
       </c>
       <c r="M103" s="6" t="inlineStr"/>
@@ -4978,42 +4978,40 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>HATEK</t>
+          <t>AVGYO</t>
         </is>
       </c>
       <c r="B104" s="3" t="n">
-        <v>16.39</v>
+        <v>12.13</v>
       </c>
       <c r="C104" s="4" t="n">
-        <v>0.04389999999999999</v>
+        <v>-0.0358</v>
       </c>
       <c r="D104" s="5" t="n">
-        <v>3910000</v>
+        <v>1600000</v>
       </c>
       <c r="E104" s="4" t="n">
-        <v>0.6177</v>
+        <v>0.7618</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>52.27</v>
+        <v>43.18</v>
       </c>
       <c r="G104" s="2" t="inlineStr"/>
       <c r="H104" s="3" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="I104" s="4" t="n">
-        <v>-0.0335</v>
-      </c>
-      <c r="J104" s="4" t="n">
-        <v>-1.222</v>
-      </c>
+        <v>-0.0146</v>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TEKSTİL DERİ, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST ANA</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr"/>
@@ -5021,42 +5019,42 @@
     <row r="105">
       <c r="A105" s="6" t="inlineStr">
         <is>
-          <t>AGHOL</t>
+          <t>HATEK</t>
         </is>
       </c>
       <c r="B105" s="7" t="n">
-        <v>34.3</v>
+        <v>16.39</v>
       </c>
       <c r="C105" s="8" t="n">
-        <v>0.0076</v>
+        <v>0.04389999999999999</v>
       </c>
       <c r="D105" s="9" t="n">
-        <v>6530000</v>
+        <v>3910000</v>
       </c>
       <c r="E105" s="8" t="n">
-        <v>0.5135000000000001</v>
+        <v>0.6177</v>
       </c>
       <c r="F105" s="7" t="n">
-        <v>55.58</v>
-      </c>
-      <c r="G105" s="7" t="n">
-        <v>22.84</v>
-      </c>
+        <v>52.27</v>
+      </c>
+      <c r="G105" s="6" t="inlineStr"/>
       <c r="H105" s="7" t="n">
         <v>0.66</v>
       </c>
       <c r="I105" s="8" t="n">
-        <v>0.0341</v>
-      </c>
-      <c r="J105" s="6" t="inlineStr"/>
+        <v>-0.0335</v>
+      </c>
+      <c r="J105" s="8" t="n">
+        <v>-1.222</v>
+      </c>
       <c r="K105" s="6" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="L105" s="6" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU 25, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, STOXX Emerging Markets 1500</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TEKSTİL DERİ, BIST ANA</t>
         </is>
       </c>
       <c r="M105" s="6" t="inlineStr"/>
@@ -5064,42 +5062,42 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>PLTUR</t>
+          <t>AGHOL</t>
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>23.32</v>
+        <v>34.3</v>
       </c>
       <c r="C106" s="4" t="n">
-        <v>-0.0185</v>
+        <v>0.0076</v>
       </c>
       <c r="D106" s="5" t="n">
-        <v>3070000</v>
+        <v>6530000</v>
       </c>
       <c r="E106" s="4" t="n">
-        <v>0.3101</v>
+        <v>0.5135000000000001</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>37.06</v>
+        <v>55.58</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>8.35</v>
+        <v>22.84</v>
       </c>
       <c r="H106" s="3" t="n">
         <v>0.66</v>
       </c>
       <c r="I106" s="4" t="n">
-        <v>0.0926</v>
+        <v>0.0341</v>
       </c>
       <c r="J106" s="2" t="inlineStr"/>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>Taşımacılık</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEMETTU, BIST KATILIM TEMETTU</t>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU 25, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, STOXX Emerging Markets 1500</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr"/>
@@ -5107,44 +5105,42 @@
     <row r="107">
       <c r="A107" s="6" t="inlineStr">
         <is>
-          <t>INVEO</t>
+          <t>PLTUR</t>
         </is>
       </c>
       <c r="B107" s="7" t="n">
-        <v>8.369999999999999</v>
+        <v>23.32</v>
       </c>
       <c r="C107" s="8" t="n">
-        <v>-0.099</v>
+        <v>-0.0185</v>
       </c>
       <c r="D107" s="9" t="n">
-        <v>20490000</v>
+        <v>3070000</v>
       </c>
       <c r="E107" s="8" t="n">
-        <v>0.1898</v>
+        <v>0.3101</v>
       </c>
       <c r="F107" s="7" t="n">
-        <v>55.55</v>
+        <v>37.06</v>
       </c>
       <c r="G107" s="7" t="n">
-        <v>2.91</v>
+        <v>8.35</v>
       </c>
       <c r="H107" s="7" t="n">
         <v>0.66</v>
       </c>
       <c r="I107" s="8" t="n">
-        <v>0.2986</v>
-      </c>
-      <c r="J107" s="8" t="n">
-        <v>-1.5684</v>
-      </c>
+        <v>0.0926</v>
+      </c>
+      <c r="J107" s="6" t="inlineStr"/>
       <c r="K107" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Taşımacılık</t>
         </is>
       </c>
       <c r="L107" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST YILDIZ</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEMETTU, BIST KATILIM TEMETTU</t>
         </is>
       </c>
       <c r="M107" s="6" t="inlineStr"/>
@@ -5152,44 +5148,44 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>AFYON</t>
+          <t>INVEO</t>
         </is>
       </c>
       <c r="B108" s="3" t="n">
-        <v>12.75</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="C108" s="4" t="n">
-        <v>-0.0132</v>
+        <v>-0.099</v>
       </c>
       <c r="D108" s="5" t="n">
-        <v>2480000</v>
+        <v>20490000</v>
       </c>
       <c r="E108" s="4" t="n">
-        <v>0.49</v>
+        <v>0.1898</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>30.45</v>
+        <v>55.55</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>68.33</v>
+        <v>2.91</v>
       </c>
       <c r="H108" s="3" t="n">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="I108" s="4" t="n">
-        <v>0.0107</v>
+        <v>0.2986</v>
       </c>
       <c r="J108" s="4" t="n">
-        <v>-1.432</v>
+        <v>-1.5684</v>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST ANA, BIST TEMETTU</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr"/>
@@ -5197,40 +5193,44 @@
     <row r="109">
       <c r="A109" s="6" t="inlineStr">
         <is>
-          <t>GSDDE</t>
+          <t>AFYON</t>
         </is>
       </c>
       <c r="B109" s="7" t="n">
-        <v>12.42</v>
+        <v>12.75</v>
       </c>
       <c r="C109" s="8" t="n">
-        <v>-0.022</v>
+        <v>-0.0132</v>
       </c>
       <c r="D109" s="9" t="n">
-        <v>21590000</v>
-      </c>
-      <c r="E109" s="6" t="inlineStr"/>
+        <v>2480000</v>
+      </c>
+      <c r="E109" s="8" t="n">
+        <v>0.49</v>
+      </c>
       <c r="F109" s="7" t="n">
-        <v>47.68</v>
+        <v>30.45</v>
       </c>
       <c r="G109" s="7" t="n">
-        <v>9.369999999999999</v>
+        <v>68.33</v>
       </c>
       <c r="H109" s="7" t="n">
         <v>0.67</v>
       </c>
       <c r="I109" s="8" t="n">
-        <v>0.0795</v>
-      </c>
-      <c r="J109" s="6" t="inlineStr"/>
+        <v>0.0107</v>
+      </c>
+      <c r="J109" s="8" t="n">
+        <v>-1.432</v>
+      </c>
       <c r="K109" s="6" t="inlineStr">
         <is>
-          <t>Taşımacılık</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="L109" s="6" t="inlineStr">
         <is>
-          <t>BIST ULASTIRMA, BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST ANA</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST ANA, BIST TEMETTU</t>
         </is>
       </c>
       <c r="M109" s="6" t="inlineStr"/>
@@ -5238,42 +5238,40 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>OYLUM</t>
+          <t>GSDDE</t>
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>8.460000000000001</v>
+        <v>12.42</v>
       </c>
       <c r="C110" s="4" t="n">
-        <v>0.0024</v>
+        <v>-0.022</v>
       </c>
       <c r="D110" s="5" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="E110" s="4" t="n">
-        <v>0.3662</v>
-      </c>
+        <v>21590000</v>
+      </c>
+      <c r="E110" s="2" t="inlineStr"/>
       <c r="F110" s="3" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="G110" s="2" t="inlineStr"/>
+        <v>47.68</v>
+      </c>
+      <c r="G110" s="3" t="n">
+        <v>9.369999999999999</v>
+      </c>
       <c r="H110" s="3" t="n">
         <v>0.67</v>
       </c>
       <c r="I110" s="4" t="n">
-        <v>-0.0946</v>
-      </c>
-      <c r="J110" s="4" t="n">
-        <v>-1.7395</v>
-      </c>
+        <v>0.0795</v>
+      </c>
+      <c r="J110" s="2" t="inlineStr"/>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Taşımacılık</t>
         </is>
       </c>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST KAYSERİ</t>
+          <t>BIST ULASTIRMA, BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST ANA</t>
         </is>
       </c>
       <c r="M110" s="2" t="inlineStr"/>
@@ -5281,42 +5279,42 @@
     <row r="111">
       <c r="A111" s="6" t="inlineStr">
         <is>
-          <t>AKENR</t>
+          <t>OYLUM</t>
         </is>
       </c>
       <c r="B111" s="7" t="n">
-        <v>11.95</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="C111" s="8" t="n">
-        <v>-0.0508</v>
+        <v>0.0024</v>
       </c>
       <c r="D111" s="9" t="n">
-        <v>42540000</v>
+        <v>1500000</v>
       </c>
       <c r="E111" s="8" t="n">
-        <v>0.2528</v>
+        <v>0.3662</v>
       </c>
       <c r="F111" s="7" t="n">
-        <v>54.71</v>
+        <v>52.9</v>
       </c>
       <c r="G111" s="6" t="inlineStr"/>
       <c r="H111" s="7" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="I111" s="8" t="n">
-        <v>-0.4023</v>
+        <v>-0.0946</v>
       </c>
       <c r="J111" s="8" t="n">
-        <v>-13.642</v>
+        <v>-1.7395</v>
       </c>
       <c r="K111" s="6" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="L111" s="6" t="inlineStr">
         <is>
-          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM</t>
+          <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST KAYSERİ</t>
         </is>
       </c>
       <c r="M111" s="6" t="inlineStr"/>
@@ -15422,40 +15420,44 @@
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>GOODY</t>
+          <t>GESAN</t>
         </is>
       </c>
       <c r="B344" s="3" t="n">
-        <v>16.63</v>
+        <v>63.8</v>
       </c>
       <c r="C344" s="4" t="n">
-        <v>0.0073</v>
+        <v>0.1</v>
       </c>
       <c r="D344" s="5" t="n">
-        <v>3190000</v>
+        <v>19760000</v>
       </c>
       <c r="E344" s="4" t="n">
-        <v>0.254</v>
+        <v>0.3082</v>
       </c>
       <c r="F344" s="3" t="n">
-        <v>58.64</v>
-      </c>
-      <c r="G344" s="2" t="inlineStr"/>
+        <v>67.70999999999999</v>
+      </c>
+      <c r="G344" s="3" t="n">
+        <v>32.41</v>
+      </c>
       <c r="H344" s="3" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="I344" s="4" t="n">
-        <v>-0.9054000000000001</v>
-      </c>
-      <c r="J344" s="2" t="inlineStr"/>
+        <v>0.0684</v>
+      </c>
+      <c r="J344" s="4" t="n">
+        <v>1.0708</v>
+      </c>
       <c r="K344" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı tüketim malları</t>
+          <t>Elektronik teknoloji</t>
         </is>
       </c>
       <c r="L344" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST İNŞAAT, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST ANKARA</t>
         </is>
       </c>
       <c r="M344" s="2" t="inlineStr"/>
@@ -15463,42 +15465,40 @@
     <row r="345">
       <c r="A345" s="6" t="inlineStr">
         <is>
-          <t>ISYAT</t>
+          <t>GOODY</t>
         </is>
       </c>
       <c r="B345" s="7" t="n">
-        <v>8.18</v>
+        <v>16.63</v>
       </c>
       <c r="C345" s="8" t="n">
-        <v>-0.0121</v>
+        <v>0.0073</v>
       </c>
       <c r="D345" s="9" t="n">
-        <v>2570000</v>
+        <v>3190000</v>
       </c>
       <c r="E345" s="8" t="n">
-        <v>0.6434000000000001</v>
+        <v>0.254</v>
       </c>
       <c r="F345" s="7" t="n">
-        <v>40.78</v>
-      </c>
-      <c r="G345" s="7" t="n">
-        <v>192.02</v>
-      </c>
+        <v>58.64</v>
+      </c>
+      <c r="G345" s="6" t="inlineStr"/>
       <c r="H345" s="7" t="n">
         <v>1.93</v>
       </c>
       <c r="I345" s="8" t="n">
-        <v>0.0114</v>
+        <v>-0.9054000000000001</v>
       </c>
       <c r="J345" s="6" t="inlineStr"/>
       <c r="K345" s="6" t="inlineStr">
         <is>
-          <t>Çeşitli Hizmetler</t>
+          <t>Dayanıklı tüketim malları</t>
         </is>
       </c>
       <c r="L345" s="6" t="inlineStr">
         <is>
-          <t>BIST MENKUL KIYM YO</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M345" s="6" t="inlineStr"/>
@@ -15506,42 +15506,42 @@
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>LUKSK</t>
+          <t>ISYAT</t>
         </is>
       </c>
       <c r="B346" s="3" t="n">
-        <v>103.9</v>
+        <v>8.18</v>
       </c>
       <c r="C346" s="4" t="n">
-        <v>-0.005699999999999999</v>
+        <v>-0.0121</v>
       </c>
       <c r="D346" s="5" t="n">
-        <v>183070</v>
+        <v>2570000</v>
       </c>
       <c r="E346" s="4" t="n">
-        <v>0.1987</v>
+        <v>0.6434000000000001</v>
       </c>
       <c r="F346" s="3" t="n">
-        <v>45.9</v>
+        <v>40.78</v>
       </c>
       <c r="G346" s="3" t="n">
-        <v>78.52</v>
+        <v>192.02</v>
       </c>
       <c r="H346" s="3" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="I346" s="4" t="n">
-        <v>0.0283</v>
+        <v>0.0114</v>
       </c>
       <c r="J346" s="2" t="inlineStr"/>
       <c r="K346" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Çeşitli Hizmetler</t>
         </is>
       </c>
       <c r="L346" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TEKSTİL DERİ, BIST ANA, BIST KOBİ SANAYİ, BIST KAYSERİ</t>
+          <t>BIST MENKUL KIYM YO</t>
         </is>
       </c>
       <c r="M346" s="2" t="inlineStr"/>
@@ -15549,40 +15549,42 @@
     <row r="347">
       <c r="A347" s="6" t="inlineStr">
         <is>
-          <t>BJKAS</t>
+          <t>LUKSK</t>
         </is>
       </c>
       <c r="B347" s="7" t="n">
-        <v>1.56</v>
+        <v>103.9</v>
       </c>
       <c r="C347" s="8" t="n">
-        <v>-0.0189</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="D347" s="9" t="n">
-        <v>160980000</v>
+        <v>183070</v>
       </c>
       <c r="E347" s="8" t="n">
-        <v>0.2988</v>
+        <v>0.1987</v>
       </c>
       <c r="F347" s="7" t="n">
-        <v>44.55</v>
-      </c>
-      <c r="G347" s="6" t="inlineStr"/>
+        <v>45.9</v>
+      </c>
+      <c r="G347" s="7" t="n">
+        <v>78.52</v>
+      </c>
       <c r="H347" s="7" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="I347" s="8" t="n">
-        <v>-4.0666</v>
+        <v>0.0283</v>
       </c>
       <c r="J347" s="6" t="inlineStr"/>
       <c r="K347" s="6" t="inlineStr">
         <is>
-          <t>Tüketici hizmetleri</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="L347" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST SPOR, BIST HİZMETLER, BIST İSTANBUL, BIST YILDIZ</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TEKSTİL DERİ, BIST ANA, BIST KOBİ SANAYİ, BIST KAYSERİ</t>
         </is>
       </c>
       <c r="M347" s="6" t="inlineStr"/>
@@ -15590,44 +15592,40 @@
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>GLCVY</t>
+          <t>BJKAS</t>
         </is>
       </c>
       <c r="B348" s="3" t="n">
-        <v>59.85</v>
+        <v>1.56</v>
       </c>
       <c r="C348" s="4" t="n">
-        <v>-0.0075</v>
+        <v>-0.0189</v>
       </c>
       <c r="D348" s="5" t="n">
-        <v>1350000</v>
+        <v>160980000</v>
       </c>
       <c r="E348" s="4" t="n">
-        <v>0.189</v>
+        <v>0.2988</v>
       </c>
       <c r="F348" s="3" t="n">
-        <v>39.04</v>
-      </c>
-      <c r="G348" s="3" t="n">
-        <v>5.4</v>
-      </c>
+        <v>44.55</v>
+      </c>
+      <c r="G348" s="2" t="inlineStr"/>
       <c r="H348" s="3" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="I348" s="4" t="n">
-        <v>0.4245</v>
-      </c>
-      <c r="J348" s="4" t="n">
-        <v>0.1038</v>
-      </c>
+        <v>-4.0666</v>
+      </c>
+      <c r="J348" s="2" t="inlineStr"/>
       <c r="K348" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Tüketici hizmetleri</t>
         </is>
       </c>
       <c r="L348" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST MALİ, BIST YILDIZ, BIST TEMETTU</t>
+          <t>BIST TUM-100, BIST TÜM, BIST SPOR, BIST HİZMETLER, BIST İSTANBUL, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M348" s="2" t="inlineStr"/>
@@ -15635,44 +15633,44 @@
     <row r="349">
       <c r="A349" s="6" t="inlineStr">
         <is>
-          <t>EGPRO</t>
+          <t>GLCVY</t>
         </is>
       </c>
       <c r="B349" s="7" t="n">
-        <v>36.7</v>
+        <v>59.85</v>
       </c>
       <c r="C349" s="8" t="n">
-        <v>-0.0585</v>
+        <v>-0.0075</v>
       </c>
       <c r="D349" s="9" t="n">
-        <v>1950000</v>
+        <v>1350000</v>
       </c>
       <c r="E349" s="8" t="n">
-        <v>0.1314</v>
+        <v>0.189</v>
       </c>
       <c r="F349" s="7" t="n">
-        <v>43.59</v>
+        <v>39.04</v>
       </c>
       <c r="G349" s="7" t="n">
-        <v>16.4</v>
+        <v>5.4</v>
       </c>
       <c r="H349" s="7" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="I349" s="8" t="n">
-        <v>0.1433</v>
+        <v>0.4245</v>
       </c>
       <c r="J349" s="8" t="n">
-        <v>-0.2049</v>
+        <v>0.1038</v>
       </c>
       <c r="K349" s="6" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L349" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST KATILIM TÜM, BIST YILDIZ, BIST TEMETTU, BIST KATILIM TEMETTU, BIST İZMİR</t>
+          <t>BIST TUM-100, BIST TÜM, BIST MALİ, BIST YILDIZ, BIST TEMETTU</t>
         </is>
       </c>
       <c r="M349" s="6" t="inlineStr"/>
@@ -15680,44 +15678,44 @@
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>PCILT</t>
+          <t>EGPRO</t>
         </is>
       </c>
       <c r="B350" s="3" t="n">
-        <v>33</v>
+        <v>36.7</v>
       </c>
       <c r="C350" s="4" t="n">
-        <v>0.0248</v>
+        <v>-0.0585</v>
       </c>
       <c r="D350" s="5" t="n">
-        <v>3360000</v>
+        <v>1950000</v>
       </c>
       <c r="E350" s="4" t="n">
-        <v>0.5865</v>
+        <v>0.1314</v>
       </c>
       <c r="F350" s="3" t="n">
-        <v>64.02</v>
+        <v>43.59</v>
       </c>
       <c r="G350" s="3" t="n">
-        <v>8.369999999999999</v>
+        <v>16.4</v>
       </c>
       <c r="H350" s="3" t="n">
         <v>1.99</v>
       </c>
       <c r="I350" s="4" t="n">
-        <v>0.2928</v>
+        <v>0.1433</v>
       </c>
       <c r="J350" s="4" t="n">
-        <v>0.6712</v>
+        <v>-0.2049</v>
       </c>
       <c r="K350" s="2" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="L350" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST TEMETTU</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST KATILIM TÜM, BIST YILDIZ, BIST TEMETTU, BIST KATILIM TEMETTU, BIST İZMİR</t>
         </is>
       </c>
       <c r="M350" s="2" t="inlineStr"/>
@@ -15725,42 +15723,44 @@
     <row r="351">
       <c r="A351" s="6" t="inlineStr">
         <is>
-          <t>EKSUN</t>
+          <t>PCILT</t>
         </is>
       </c>
       <c r="B351" s="7" t="n">
-        <v>7.73</v>
+        <v>33</v>
       </c>
       <c r="C351" s="8" t="n">
-        <v>0.0362</v>
+        <v>0.0248</v>
       </c>
       <c r="D351" s="9" t="n">
-        <v>15570000</v>
+        <v>3360000</v>
       </c>
       <c r="E351" s="8" t="n">
-        <v>0.2726</v>
+        <v>0.5865</v>
       </c>
       <c r="F351" s="7" t="n">
-        <v>78.7</v>
-      </c>
-      <c r="G351" s="6" t="inlineStr"/>
+        <v>64.02</v>
+      </c>
+      <c r="G351" s="7" t="n">
+        <v>8.369999999999999</v>
+      </c>
       <c r="H351" s="7" t="n">
         <v>1.99</v>
       </c>
       <c r="I351" s="8" t="n">
-        <v>-0.1422</v>
+        <v>0.2928</v>
       </c>
       <c r="J351" s="8" t="n">
-        <v>0.5267000000000001</v>
+        <v>0.6712</v>
       </c>
       <c r="K351" s="6" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Ticari hizmetler</t>
         </is>
       </c>
       <c r="L351" s="6" t="inlineStr">
         <is>
-          <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST KATILIM TÜM, BIST ANA, BIST TEKİRDAĞ</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST TEMETTU</t>
         </is>
       </c>
       <c r="M351" s="6" t="inlineStr"/>
@@ -15768,35 +15768,33 @@
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>OFSYM</t>
+          <t>EKSUN</t>
         </is>
       </c>
       <c r="B352" s="3" t="n">
-        <v>56.2</v>
+        <v>7.73</v>
       </c>
       <c r="C352" s="4" t="n">
-        <v>-0.026</v>
+        <v>0.0362</v>
       </c>
       <c r="D352" s="5" t="n">
-        <v>2420000</v>
+        <v>15570000</v>
       </c>
       <c r="E352" s="4" t="n">
-        <v>0.1556</v>
+        <v>0.2726</v>
       </c>
       <c r="F352" s="3" t="n">
-        <v>40.07</v>
-      </c>
-      <c r="G352" s="3" t="n">
-        <v>27.9</v>
-      </c>
+        <v>78.7</v>
+      </c>
+      <c r="G352" s="2" t="inlineStr"/>
       <c r="H352" s="3" t="n">
         <v>1.99</v>
       </c>
       <c r="I352" s="4" t="n">
-        <v>0.08449999999999999</v>
+        <v>-0.1422</v>
       </c>
       <c r="J352" s="4" t="n">
-        <v>0.1882</v>
+        <v>0.5267000000000001</v>
       </c>
       <c r="K352" s="2" t="inlineStr">
         <is>
@@ -15805,7 +15803,7 @@
       </c>
       <c r="L352" s="2" t="inlineStr">
         <is>
-          <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST ANA, BIST ANKARA</t>
+          <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST KATILIM TÜM, BIST ANA, BIST TEKİRDAĞ</t>
         </is>
       </c>
       <c r="M352" s="2" t="inlineStr"/>
@@ -15813,44 +15811,44 @@
     <row r="353">
       <c r="A353" s="6" t="inlineStr">
         <is>
-          <t>ORGE</t>
+          <t>OFSYM</t>
         </is>
       </c>
       <c r="B353" s="7" t="n">
-        <v>102.4</v>
+        <v>56.2</v>
       </c>
       <c r="C353" s="8" t="n">
-        <v>0.0993</v>
+        <v>-0.026</v>
       </c>
       <c r="D353" s="9" t="n">
-        <v>2540000</v>
+        <v>2420000</v>
       </c>
       <c r="E353" s="8" t="n">
-        <v>0.4719</v>
+        <v>0.1556</v>
       </c>
       <c r="F353" s="7" t="n">
-        <v>73.59999999999999</v>
+        <v>40.07</v>
       </c>
       <c r="G353" s="7" t="n">
-        <v>14.15</v>
+        <v>27.9</v>
       </c>
       <c r="H353" s="7" t="n">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="I353" s="8" t="n">
-        <v>0.1767</v>
+        <v>0.08449999999999999</v>
       </c>
       <c r="J353" s="8" t="n">
-        <v>0.8362999999999999</v>
+        <v>0.1882</v>
       </c>
       <c r="K353" s="6" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="L353" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST İNŞAAT, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ</t>
+          <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST ANA, BIST ANKARA</t>
         </is>
       </c>
       <c r="M353" s="6" t="inlineStr"/>
@@ -15858,42 +15856,44 @@
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>SONME</t>
+          <t>ORGE</t>
         </is>
       </c>
       <c r="B354" s="3" t="n">
-        <v>129.9</v>
+        <v>102.4</v>
       </c>
       <c r="C354" s="4" t="n">
-        <v>-0.0328</v>
+        <v>0.0993</v>
       </c>
       <c r="D354" s="5" t="n">
-        <v>49970</v>
+        <v>2540000</v>
       </c>
       <c r="E354" s="4" t="n">
-        <v>0.0789</v>
+        <v>0.4719</v>
       </c>
       <c r="F354" s="3" t="n">
-        <v>33.59</v>
-      </c>
-      <c r="G354" s="2" t="inlineStr"/>
+        <v>73.59999999999999</v>
+      </c>
+      <c r="G354" s="3" t="n">
+        <v>14.15</v>
+      </c>
       <c r="H354" s="3" t="n">
         <v>2.05</v>
       </c>
       <c r="I354" s="4" t="n">
-        <v>-0.08929999999999999</v>
+        <v>0.1767</v>
       </c>
       <c r="J354" s="4" t="n">
-        <v>0.4032</v>
+        <v>0.8362999999999999</v>
       </c>
       <c r="K354" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Endüstriyel hizmetler</t>
         </is>
       </c>
       <c r="L354" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST BURSA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST İNŞAAT, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M354" s="2" t="inlineStr"/>
@@ -15901,44 +15901,42 @@
     <row r="355">
       <c r="A355" s="6" t="inlineStr">
         <is>
-          <t>GEDIK</t>
+          <t>SONME</t>
         </is>
       </c>
       <c r="B355" s="7" t="n">
-        <v>6.91</v>
+        <v>129.9</v>
       </c>
       <c r="C355" s="8" t="n">
-        <v>-0.09910000000000001</v>
+        <v>-0.0328</v>
       </c>
       <c r="D355" s="9" t="n">
-        <v>25390000</v>
+        <v>49970</v>
       </c>
       <c r="E355" s="8" t="n">
-        <v>0.4915</v>
+        <v>0.0789</v>
       </c>
       <c r="F355" s="7" t="n">
-        <v>63.23</v>
-      </c>
-      <c r="G355" s="7" t="n">
-        <v>5.72</v>
-      </c>
+        <v>33.59</v>
+      </c>
+      <c r="G355" s="6" t="inlineStr"/>
       <c r="H355" s="7" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="I355" s="8" t="n">
-        <v>0.344</v>
+        <v>-0.08929999999999999</v>
       </c>
       <c r="J355" s="8" t="n">
-        <v>1.5455</v>
+        <v>0.4032</v>
       </c>
       <c r="K355" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="L355" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST MALİ, BIST ARACI KURUMLAR, BIST YILDIZ, BIST TEMETTU</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST BURSA</t>
         </is>
       </c>
       <c r="M355" s="6" t="inlineStr"/>
@@ -15946,40 +15944,44 @@
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>AKHAN</t>
+          <t>GEDIK</t>
         </is>
       </c>
       <c r="B356" s="3" t="n">
-        <v>28.18</v>
+        <v>6.91</v>
       </c>
       <c r="C356" s="4" t="n">
-        <v>0.027</v>
+        <v>-0.09910000000000001</v>
       </c>
       <c r="D356" s="5" t="n">
-        <v>7770000</v>
+        <v>25390000</v>
       </c>
       <c r="E356" s="4" t="n">
-        <v>0.2001</v>
+        <v>0.4915</v>
       </c>
       <c r="F356" s="3" t="n">
-        <v>51.13</v>
-      </c>
-      <c r="G356" s="2" t="inlineStr"/>
+        <v>63.23</v>
+      </c>
+      <c r="G356" s="3" t="n">
+        <v>5.72</v>
+      </c>
       <c r="H356" s="3" t="n">
         <v>2.06</v>
       </c>
       <c r="I356" s="4" t="n">
-        <v>0.0438</v>
-      </c>
-      <c r="J356" s="2" t="inlineStr"/>
+        <v>0.344</v>
+      </c>
+      <c r="J356" s="4" t="n">
+        <v>1.5455</v>
+      </c>
       <c r="K356" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L356" s="2" t="inlineStr">
         <is>
-          <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST MALİ, BIST ARACI KURUMLAR, BIST YILDIZ, BIST TEMETTU</t>
         </is>
       </c>
       <c r="M356" s="2" t="inlineStr"/>
@@ -15987,42 +15989,40 @@
     <row r="357">
       <c r="A357" s="6" t="inlineStr">
         <is>
-          <t>HURGZ</t>
+          <t>AKHAN</t>
         </is>
       </c>
       <c r="B357" s="7" t="n">
-        <v>8</v>
+        <v>28.18</v>
       </c>
       <c r="C357" s="8" t="n">
-        <v>-0.08779999999999999</v>
+        <v>0.027</v>
       </c>
       <c r="D357" s="9" t="n">
-        <v>25630000</v>
+        <v>7770000</v>
       </c>
       <c r="E357" s="8" t="n">
-        <v>0.1879</v>
+        <v>0.2001</v>
       </c>
       <c r="F357" s="7" t="n">
-        <v>51.81</v>
+        <v>51.13</v>
       </c>
       <c r="G357" s="6" t="inlineStr"/>
       <c r="H357" s="7" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="I357" s="8" t="n">
-        <v>-0.4406</v>
-      </c>
-      <c r="J357" s="8" t="n">
-        <v>-11.3341</v>
-      </c>
+        <v>0.0438</v>
+      </c>
+      <c r="J357" s="6" t="inlineStr"/>
       <c r="K357" s="6" t="inlineStr">
         <is>
-          <t>Tüketici hizmetleri</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="L357" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST KURUMSAL YÖNETİM</t>
+          <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M357" s="6" t="inlineStr"/>
@@ -16030,44 +16030,42 @@
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>SEGMN</t>
+          <t>HURGZ</t>
         </is>
       </c>
       <c r="B358" s="3" t="n">
-        <v>58.7</v>
+        <v>8</v>
       </c>
       <c r="C358" s="4" t="n">
-        <v>-0.04940000000000001</v>
+        <v>-0.08779999999999999</v>
       </c>
       <c r="D358" s="5" t="n">
-        <v>5090000</v>
+        <v>25630000</v>
       </c>
       <c r="E358" s="4" t="n">
-        <v>0.2515</v>
+        <v>0.1879</v>
       </c>
       <c r="F358" s="3" t="n">
-        <v>47.41</v>
-      </c>
-      <c r="G358" s="3" t="n">
-        <v>38.33</v>
-      </c>
+        <v>51.81</v>
+      </c>
+      <c r="G358" s="2" t="inlineStr"/>
       <c r="H358" s="3" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="I358" s="4" t="n">
-        <v>0.0669</v>
+        <v>-0.4406</v>
       </c>
       <c r="J358" s="4" t="n">
-        <v>4.7457</v>
+        <v>-11.3341</v>
       </c>
       <c r="K358" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Tüketici hizmetleri</t>
         </is>
       </c>
       <c r="L358" s="2" t="inlineStr">
         <is>
-          <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST HALKA ARZ, BIST ANA, BIST ANKARA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST KURUMSAL YÖNETİM</t>
         </is>
       </c>
       <c r="M358" s="2" t="inlineStr"/>
@@ -16075,42 +16073,44 @@
     <row r="359">
       <c r="A359" s="6" t="inlineStr">
         <is>
-          <t>EGEEN</t>
-        </is>
-      </c>
-      <c r="B359" s="9" t="n">
-        <v>5650</v>
+          <t>SEGMN</t>
+        </is>
+      </c>
+      <c r="B359" s="7" t="n">
+        <v>58.7</v>
       </c>
       <c r="C359" s="8" t="n">
-        <v>-0.0309</v>
+        <v>-0.04940000000000001</v>
       </c>
       <c r="D359" s="9" t="n">
-        <v>17950</v>
+        <v>5090000</v>
       </c>
       <c r="E359" s="8" t="n">
-        <v>0.3637</v>
+        <v>0.2515</v>
       </c>
       <c r="F359" s="7" t="n">
-        <v>34.95</v>
-      </c>
-      <c r="G359" s="6" t="inlineStr"/>
+        <v>47.41</v>
+      </c>
+      <c r="G359" s="7" t="n">
+        <v>38.33</v>
+      </c>
       <c r="H359" s="7" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="I359" s="8" t="n">
-        <v>-0.0341</v>
+        <v>0.0669</v>
       </c>
       <c r="J359" s="8" t="n">
-        <v>0.3126</v>
+        <v>4.7457</v>
       </c>
       <c r="K359" s="6" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="L359" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST YILDIZ, BIST İZMİR</t>
+          <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST HALKA ARZ, BIST ANA, BIST ANKARA</t>
         </is>
       </c>
       <c r="M359" s="6" t="inlineStr"/>
@@ -16118,44 +16118,42 @@
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>BEYAZ</t>
-        </is>
-      </c>
-      <c r="B360" s="3" t="n">
-        <v>28.2</v>
+          <t>EGEEN</t>
+        </is>
+      </c>
+      <c r="B360" s="5" t="n">
+        <v>5650</v>
       </c>
       <c r="C360" s="4" t="n">
-        <v>0.0028</v>
+        <v>-0.0309</v>
       </c>
       <c r="D360" s="5" t="n">
-        <v>1050000</v>
+        <v>17950</v>
       </c>
       <c r="E360" s="4" t="n">
-        <v>0.2455</v>
+        <v>0.3637</v>
       </c>
       <c r="F360" s="3" t="n">
-        <v>39.89</v>
-      </c>
-      <c r="G360" s="3" t="n">
-        <v>22.06</v>
-      </c>
+        <v>34.95</v>
+      </c>
+      <c r="G360" s="2" t="inlineStr"/>
       <c r="H360" s="3" t="n">
         <v>2.11</v>
       </c>
       <c r="I360" s="4" t="n">
-        <v>0.1128</v>
+        <v>-0.0341</v>
       </c>
       <c r="J360" s="4" t="n">
-        <v>-0.9066</v>
+        <v>0.3126</v>
       </c>
       <c r="K360" s="2" t="inlineStr">
         <is>
-          <t>Perakende satış</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="L360" s="2" t="inlineStr">
         <is>
-          <t>BIST ULASTIRMA, BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST ANA, BIST BALIKESİR</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST YILDIZ, BIST İZMİR</t>
         </is>
       </c>
       <c r="M360" s="2" t="inlineStr"/>
@@ -16163,40 +16161,44 @@
     <row r="361">
       <c r="A361" s="6" t="inlineStr">
         <is>
-          <t>SEYKM</t>
+          <t>BEYAZ</t>
         </is>
       </c>
       <c r="B361" s="7" t="n">
-        <v>5.31</v>
+        <v>28.2</v>
       </c>
       <c r="C361" s="8" t="n">
-        <v>-0.0221</v>
-      </c>
-      <c r="D361" s="7" t="n">
-        <v>4030000</v>
-      </c>
-      <c r="E361" s="6" t="inlineStr"/>
+        <v>0.0028</v>
+      </c>
+      <c r="D361" s="9" t="n">
+        <v>1050000</v>
+      </c>
+      <c r="E361" s="8" t="n">
+        <v>0.2455</v>
+      </c>
       <c r="F361" s="7" t="n">
-        <v>54</v>
-      </c>
-      <c r="G361" s="6" t="inlineStr"/>
+        <v>39.89</v>
+      </c>
+      <c r="G361" s="7" t="n">
+        <v>22.06</v>
+      </c>
       <c r="H361" s="7" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="I361" s="8" t="n">
-        <v>-0.0332</v>
+        <v>0.1128</v>
       </c>
       <c r="J361" s="8" t="n">
-        <v>-0.8992</v>
+        <v>-0.9066</v>
       </c>
       <c r="K361" s="6" t="inlineStr">
         <is>
-          <t>Sağlık teknolojisi</t>
+          <t>Perakende satış</t>
         </is>
       </c>
       <c r="L361" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST KOBİ SANAYİ, BIST MANİSA</t>
+          <t>BIST ULASTIRMA, BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST ANA, BIST BALIKESİR</t>
         </is>
       </c>
       <c r="M361" s="6" t="inlineStr"/>
@@ -16204,40 +16206,40 @@
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>KNFRT</t>
+          <t>SEYKM</t>
         </is>
       </c>
       <c r="B362" s="3" t="n">
-        <v>11.9</v>
+        <v>5.31</v>
       </c>
       <c r="C362" s="4" t="n">
-        <v>-0.0294</v>
-      </c>
-      <c r="D362" s="5" t="n">
-        <v>4490000</v>
-      </c>
-      <c r="E362" s="4" t="n">
-        <v>0.2239</v>
-      </c>
+        <v>-0.0221</v>
+      </c>
+      <c r="D362" s="3" t="n">
+        <v>4030000</v>
+      </c>
+      <c r="E362" s="2" t="inlineStr"/>
       <c r="F362" s="3" t="n">
-        <v>46.89</v>
+        <v>54</v>
       </c>
       <c r="G362" s="2" t="inlineStr"/>
       <c r="H362" s="3" t="n">
         <v>2.15</v>
       </c>
       <c r="I362" s="4" t="n">
-        <v>-0.09710000000000001</v>
-      </c>
-      <c r="J362" s="2" t="inlineStr"/>
+        <v>-0.0332</v>
+      </c>
+      <c r="J362" s="4" t="n">
+        <v>-0.8992</v>
+      </c>
       <c r="K362" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Sağlık teknolojisi</t>
         </is>
       </c>
       <c r="L362" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST KOBİ SANAYİ, BIST MANİSA</t>
         </is>
       </c>
       <c r="M362" s="2" t="inlineStr"/>
@@ -16245,44 +16247,40 @@
     <row r="363">
       <c r="A363" s="6" t="inlineStr">
         <is>
-          <t>GESAN</t>
+          <t>KNFRT</t>
         </is>
       </c>
       <c r="B363" s="7" t="n">
-        <v>63.8</v>
+        <v>11.9</v>
       </c>
       <c r="C363" s="8" t="n">
-        <v>0.1</v>
+        <v>-0.0294</v>
       </c>
       <c r="D363" s="9" t="n">
-        <v>19760000</v>
+        <v>4490000</v>
       </c>
       <c r="E363" s="8" t="n">
-        <v>0.3082</v>
+        <v>0.2239</v>
       </c>
       <c r="F363" s="7" t="n">
-        <v>67.70999999999999</v>
-      </c>
-      <c r="G363" s="7" t="n">
-        <v>25.82</v>
-      </c>
+        <v>46.89</v>
+      </c>
+      <c r="G363" s="6" t="inlineStr"/>
       <c r="H363" s="7" t="n">
         <v>2.15</v>
       </c>
       <c r="I363" s="8" t="n">
-        <v>0.09720000000000001</v>
-      </c>
-      <c r="J363" s="8" t="n">
-        <v>-0.8568000000000001</v>
-      </c>
+        <v>-0.09710000000000001</v>
+      </c>
+      <c r="J363" s="6" t="inlineStr"/>
       <c r="K363" s="6" t="inlineStr">
         <is>
-          <t>Elektronik teknoloji</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="L363" s="6" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST İNŞAAT, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST ANKARA</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M363" s="6" t="inlineStr"/>
@@ -25905,40 +25903,34 @@
     <row r="587">
       <c r="A587" s="6" t="inlineStr">
         <is>
-          <t>VKING</t>
+          <t>INTEK</t>
         </is>
       </c>
       <c r="B587" s="7" t="n">
-        <v>25.2</v>
+        <v>234</v>
       </c>
       <c r="C587" s="8" t="n">
-        <v>-0.0315</v>
+        <v>-0.0254</v>
       </c>
       <c r="D587" s="9" t="n">
-        <v>857620</v>
+        <v>10360</v>
       </c>
       <c r="E587" s="8" t="n">
-        <v>0.9698</v>
+        <v>0.2578</v>
       </c>
       <c r="F587" s="7" t="n">
-        <v>38.25</v>
+        <v>39.91</v>
       </c>
       <c r="G587" s="6" t="inlineStr"/>
       <c r="H587" s="6" t="inlineStr"/>
       <c r="I587" s="6" t="inlineStr"/>
-      <c r="J587" s="8" t="n">
-        <v>0.6453</v>
-      </c>
+      <c r="J587" s="6" t="inlineStr"/>
       <c r="K587" s="6" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
-        </is>
-      </c>
-      <c r="L587" s="6" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST ORMAN KAĞIT BASIM, BIST ANA, BIST İZMİR</t>
-        </is>
-      </c>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
+      <c r="L587" s="6" t="inlineStr"/>
       <c r="M587" s="6" t="inlineStr"/>
     </row>
     <row r="588">
@@ -25979,34 +25971,42 @@
     <row r="589">
       <c r="A589" s="6" t="inlineStr">
         <is>
-          <t>SMRVA</t>
+          <t>LILAK</t>
         </is>
       </c>
       <c r="B589" s="7" t="n">
-        <v>17.2</v>
+        <v>33.9</v>
       </c>
       <c r="C589" s="8" t="n">
-        <v>-0.0529</v>
+        <v>-0.0225</v>
       </c>
       <c r="D589" s="9" t="n">
-        <v>41580000</v>
-      </c>
-      <c r="E589" s="6" t="inlineStr"/>
+        <v>4990000</v>
+      </c>
+      <c r="E589" s="8" t="n">
+        <v>0.3528</v>
+      </c>
       <c r="F589" s="7" t="n">
-        <v>48.54</v>
-      </c>
-      <c r="G589" s="6" t="inlineStr"/>
+        <v>40.78</v>
+      </c>
+      <c r="G589" s="7" t="n">
+        <v>13.4</v>
+      </c>
       <c r="H589" s="6" t="inlineStr"/>
-      <c r="I589" s="6" t="inlineStr"/>
-      <c r="J589" s="6" t="inlineStr"/>
+      <c r="I589" s="8" t="n">
+        <v>0.1029</v>
+      </c>
+      <c r="J589" s="8" t="n">
+        <v>-1.4864</v>
+      </c>
       <c r="K589" s="6" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="L589" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST MALİ, BIST ANA, BIST TEMETTU</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST HALKA ARZ, BIST ORMAN KAĞIT BASIM, BIST YILDIZ, BIST TEMETTU, BIST KURUMSAL YÖNETİM, BIST TEKİRDAĞ</t>
         </is>
       </c>
       <c r="M589" s="6" t="inlineStr"/>
@@ -26014,36 +26014,40 @@
     <row r="590">
       <c r="A590" s="2" t="inlineStr">
         <is>
-          <t>UCAYM</t>
+          <t>CRFSA</t>
         </is>
       </c>
       <c r="B590" s="3" t="n">
-        <v>30.14</v>
+        <v>136.9</v>
       </c>
       <c r="C590" s="4" t="n">
-        <v>-0.0163</v>
+        <v>-0.0406</v>
       </c>
       <c r="D590" s="5" t="n">
-        <v>16090000</v>
+        <v>919670</v>
       </c>
       <c r="E590" s="4" t="n">
-        <v>0.2667</v>
+        <v>0.1071</v>
       </c>
       <c r="F590" s="3" t="n">
-        <v>50.55</v>
+        <v>44.13</v>
       </c>
       <c r="G590" s="2" t="inlineStr"/>
       <c r="H590" s="2" t="inlineStr"/>
-      <c r="I590" s="2" t="inlineStr"/>
-      <c r="J590" s="2" t="inlineStr"/>
+      <c r="I590" s="4" t="n">
+        <v>-3.6635</v>
+      </c>
+      <c r="J590" s="4" t="n">
+        <v>-0.4897</v>
+      </c>
       <c r="K590" s="2" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
+          <t>Perakende satış</t>
         </is>
       </c>
       <c r="L590" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST ANA</t>
         </is>
       </c>
       <c r="M590" s="2" t="inlineStr"/>
@@ -26051,93 +26055,93 @@
     <row r="591">
       <c r="A591" s="6" t="inlineStr">
         <is>
-          <t>GENKM</t>
+          <t>BRMEN</t>
         </is>
       </c>
       <c r="B591" s="7" t="n">
-        <v>13.5</v>
+        <v>10.58</v>
       </c>
       <c r="C591" s="8" t="n">
-        <v>-0.033</v>
+        <v>0.0655</v>
       </c>
       <c r="D591" s="9" t="n">
-        <v>28970000</v>
-      </c>
-      <c r="E591" s="6" t="inlineStr"/>
+        <v>722290</v>
+      </c>
+      <c r="E591" s="8" t="n">
+        <v>0.95</v>
+      </c>
       <c r="F591" s="7" t="n">
-        <v>44.26</v>
+        <v>64.97</v>
       </c>
       <c r="G591" s="6" t="inlineStr"/>
       <c r="H591" s="6" t="inlineStr"/>
-      <c r="I591" s="6" t="inlineStr"/>
-      <c r="J591" s="6" t="inlineStr"/>
+      <c r="I591" s="8" t="n">
+        <v>-23.6291</v>
+      </c>
+      <c r="J591" s="8" t="n">
+        <v>-0.4678</v>
+      </c>
       <c r="K591" s="6" t="inlineStr">
         <is>
           <t>İşlenebilen endüstriler</t>
         </is>
       </c>
-      <c r="L591" s="6" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST KOCAELI</t>
-        </is>
-      </c>
+      <c r="L591" s="6" t="inlineStr"/>
       <c r="M591" s="6" t="inlineStr"/>
     </row>
     <row r="592">
       <c r="A592" s="2" t="inlineStr">
         <is>
-          <t>BRMEN</t>
+          <t>MCARD</t>
         </is>
       </c>
       <c r="B592" s="3" t="n">
-        <v>10.58</v>
+        <v>186.3</v>
       </c>
       <c r="C592" s="4" t="n">
-        <v>0.0655</v>
-      </c>
-      <c r="D592" s="5" t="n">
-        <v>722290</v>
-      </c>
-      <c r="E592" s="4" t="n">
-        <v>0.95</v>
-      </c>
+        <v>-0.061</v>
+      </c>
+      <c r="D592" s="3" t="n">
+        <v>8119999.999999999</v>
+      </c>
+      <c r="E592" s="2" t="inlineStr"/>
       <c r="F592" s="3" t="n">
-        <v>64.97</v>
+        <v>55.08</v>
       </c>
       <c r="G592" s="2" t="inlineStr"/>
       <c r="H592" s="2" t="inlineStr"/>
-      <c r="I592" s="4" t="n">
-        <v>-23.6291</v>
-      </c>
-      <c r="J592" s="4" t="n">
-        <v>-0.4678</v>
-      </c>
+      <c r="I592" s="2" t="inlineStr"/>
+      <c r="J592" s="2" t="inlineStr"/>
       <c r="K592" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
-        </is>
-      </c>
-      <c r="L592" s="2" t="inlineStr"/>
+          <t>Ticari hizmetler</t>
+        </is>
+      </c>
+      <c r="L592" s="2" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEMETTU, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KATILIM TEMETTU</t>
+        </is>
+      </c>
       <c r="M592" s="2" t="inlineStr"/>
     </row>
     <row r="593">
       <c r="A593" s="6" t="inlineStr">
         <is>
-          <t>DMLKT</t>
+          <t>BESTE</t>
         </is>
       </c>
       <c r="B593" s="7" t="n">
-        <v>6.01</v>
+        <v>28.66</v>
       </c>
       <c r="C593" s="8" t="n">
-        <v>-0.0083</v>
+        <v>0.0092</v>
       </c>
       <c r="D593" s="9" t="n">
-        <v>7810000</v>
+        <v>21030000</v>
       </c>
       <c r="E593" s="6" t="inlineStr"/>
       <c r="F593" s="7" t="n">
-        <v>39.62</v>
+        <v>56.71</v>
       </c>
       <c r="G593" s="6" t="inlineStr"/>
       <c r="H593" s="6" t="inlineStr"/>
@@ -26145,30 +26149,34 @@
       <c r="J593" s="6" t="inlineStr"/>
       <c r="K593" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
-        </is>
-      </c>
-      <c r="L593" s="6" t="inlineStr"/>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
+        </is>
+      </c>
+      <c r="L593" s="6" t="inlineStr">
+        <is>
+          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
+        </is>
+      </c>
       <c r="M593" s="6" t="inlineStr"/>
     </row>
     <row r="594">
       <c r="A594" s="2" t="inlineStr">
         <is>
-          <t>CGCAM</t>
+          <t>MARMR</t>
         </is>
       </c>
       <c r="B594" s="3" t="n">
-        <v>40.22</v>
+        <v>2.79</v>
       </c>
       <c r="C594" s="4" t="n">
-        <v>-0.0496</v>
+        <v>0.022</v>
       </c>
       <c r="D594" s="5" t="n">
-        <v>5940000</v>
+        <v>136120000</v>
       </c>
       <c r="E594" s="2" t="inlineStr"/>
       <c r="F594" s="3" t="n">
-        <v>46.69</v>
+        <v>48.9</v>
       </c>
       <c r="G594" s="2" t="inlineStr"/>
       <c r="H594" s="2" t="inlineStr"/>
@@ -26176,12 +26184,12 @@
       <c r="J594" s="2" t="inlineStr"/>
       <c r="K594" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı tüketim malları</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L594" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST HALKA ARZ, BIST ANA, BIST MANİSA</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST KOCAELI</t>
         </is>
       </c>
       <c r="M594" s="2" t="inlineStr"/>
@@ -26189,79 +26197,69 @@
     <row r="595">
       <c r="A595" s="6" t="inlineStr">
         <is>
-          <t>LILAK</t>
+          <t>DMLKT</t>
         </is>
       </c>
       <c r="B595" s="7" t="n">
-        <v>33.9</v>
+        <v>6.01</v>
       </c>
       <c r="C595" s="8" t="n">
-        <v>-0.0225</v>
+        <v>-0.0083</v>
       </c>
       <c r="D595" s="9" t="n">
-        <v>4990000</v>
-      </c>
-      <c r="E595" s="8" t="n">
-        <v>0.3528</v>
-      </c>
+        <v>7810000</v>
+      </c>
+      <c r="E595" s="6" t="inlineStr"/>
       <c r="F595" s="7" t="n">
-        <v>40.78</v>
-      </c>
-      <c r="G595" s="7" t="n">
-        <v>13.4</v>
-      </c>
+        <v>39.62</v>
+      </c>
+      <c r="G595" s="6" t="inlineStr"/>
       <c r="H595" s="6" t="inlineStr"/>
-      <c r="I595" s="8" t="n">
-        <v>0.1029</v>
-      </c>
-      <c r="J595" s="8" t="n">
-        <v>-1.4864</v>
-      </c>
+      <c r="I595" s="6" t="inlineStr"/>
+      <c r="J595" s="6" t="inlineStr"/>
       <c r="K595" s="6" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
-        </is>
-      </c>
-      <c r="L595" s="6" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST HALKA ARZ, BIST ORMAN KAĞIT BASIM, BIST YILDIZ, BIST TEMETTU, BIST KURUMSAL YÖNETİM, BIST TEKİRDAĞ</t>
-        </is>
-      </c>
+          <t>Finans</t>
+        </is>
+      </c>
+      <c r="L595" s="6" t="inlineStr"/>
       <c r="M595" s="6" t="inlineStr"/>
     </row>
     <row r="596">
       <c r="A596" s="2" t="inlineStr">
         <is>
-          <t>ICUGS</t>
+          <t>VKING</t>
         </is>
       </c>
       <c r="B596" s="3" t="n">
-        <v>6.35</v>
+        <v>25.2</v>
       </c>
       <c r="C596" s="4" t="n">
-        <v>-0.014</v>
+        <v>-0.0315</v>
       </c>
       <c r="D596" s="5" t="n">
-        <v>13400000</v>
+        <v>857620</v>
       </c>
       <c r="E596" s="4" t="n">
-        <v>0.8667</v>
+        <v>0.9698</v>
       </c>
       <c r="F596" s="3" t="n">
-        <v>68.08</v>
+        <v>38.25</v>
       </c>
       <c r="G596" s="2" t="inlineStr"/>
       <c r="H596" s="2" t="inlineStr"/>
       <c r="I596" s="2" t="inlineStr"/>
-      <c r="J596" s="2" t="inlineStr"/>
+      <c r="J596" s="4" t="n">
+        <v>0.6453</v>
+      </c>
       <c r="K596" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="L596" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST MALİ, BIST ANA</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST ORMAN KAĞIT BASIM, BIST ANA, BIST İZMİR</t>
         </is>
       </c>
       <c r="M596" s="2" t="inlineStr"/>
@@ -26269,31 +26267,35 @@
     <row r="597">
       <c r="A597" s="6" t="inlineStr">
         <is>
-          <t>INTEK</t>
+          <t>MMCAS</t>
         </is>
       </c>
       <c r="B597" s="7" t="n">
-        <v>234</v>
+        <v>68</v>
       </c>
       <c r="C597" s="8" t="n">
-        <v>-0.0254</v>
+        <v>-0.0159</v>
       </c>
       <c r="D597" s="9" t="n">
-        <v>10360</v>
+        <v>46110</v>
       </c>
       <c r="E597" s="8" t="n">
-        <v>0.2578</v>
+        <v>0.58</v>
       </c>
       <c r="F597" s="7" t="n">
-        <v>39.91</v>
+        <v>35.57</v>
       </c>
       <c r="G597" s="6" t="inlineStr"/>
       <c r="H597" s="6" t="inlineStr"/>
-      <c r="I597" s="6" t="inlineStr"/>
-      <c r="J597" s="6" t="inlineStr"/>
+      <c r="I597" s="8" t="n">
+        <v>-9.409700000000001</v>
+      </c>
+      <c r="J597" s="8" t="n">
+        <v>-4.155</v>
+      </c>
       <c r="K597" s="6" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Taşımacılık</t>
         </is>
       </c>
       <c r="L597" s="6" t="inlineStr"/>
@@ -26302,21 +26304,21 @@
     <row r="598">
       <c r="A598" s="2" t="inlineStr">
         <is>
-          <t>GLRMK</t>
+          <t>FRMPL</t>
         </is>
       </c>
       <c r="B598" s="3" t="n">
-        <v>177.4</v>
+        <v>40.04</v>
       </c>
       <c r="C598" s="4" t="n">
-        <v>-0.0067</v>
-      </c>
-      <c r="D598" s="5" t="n">
-        <v>7980000</v>
+        <v>0.1</v>
+      </c>
+      <c r="D598" s="3" t="n">
+        <v>8289999.999999999</v>
       </c>
       <c r="E598" s="2" t="inlineStr"/>
       <c r="F598" s="3" t="n">
-        <v>38.18</v>
+        <v>68.78</v>
       </c>
       <c r="G598" s="2" t="inlineStr"/>
       <c r="H598" s="2" t="inlineStr"/>
@@ -26324,12 +26326,12 @@
       <c r="J598" s="2" t="inlineStr"/>
       <c r="K598" s="2" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="L598" s="2" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST ANKARA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST TEKİRDAĞ</t>
         </is>
       </c>
       <c r="M598" s="2" t="inlineStr"/>
@@ -26337,38 +26339,34 @@
     <row r="599">
       <c r="A599" s="6" t="inlineStr">
         <is>
-          <t>NETAS</t>
+          <t>GLRMK</t>
         </is>
       </c>
       <c r="B599" s="7" t="n">
-        <v>64.25</v>
+        <v>177.4</v>
       </c>
       <c r="C599" s="8" t="n">
-        <v>-0.0138</v>
+        <v>-0.0067</v>
       </c>
       <c r="D599" s="9" t="n">
-        <v>748500</v>
-      </c>
-      <c r="E599" s="8" t="n">
-        <v>0.3695000000000001</v>
-      </c>
+        <v>7980000</v>
+      </c>
+      <c r="E599" s="6" t="inlineStr"/>
       <c r="F599" s="7" t="n">
-        <v>47.67</v>
+        <v>38.18</v>
       </c>
       <c r="G599" s="6" t="inlineStr"/>
       <c r="H599" s="6" t="inlineStr"/>
       <c r="I599" s="6" t="inlineStr"/>
-      <c r="J599" s="8" t="n">
-        <v>0.1431</v>
-      </c>
+      <c r="J599" s="6" t="inlineStr"/>
       <c r="K599" s="6" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
+          <t>Endüstriyel hizmetler</t>
         </is>
       </c>
       <c r="L599" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KURUMSAL YÖNETİM</t>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST ANKARA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
         </is>
       </c>
       <c r="M599" s="6" t="inlineStr"/>
@@ -26376,21 +26374,21 @@
     <row r="600">
       <c r="A600" s="2" t="inlineStr">
         <is>
-          <t>ENPRA</t>
+          <t>SMRVA</t>
         </is>
       </c>
       <c r="B600" s="3" t="n">
-        <v>70</v>
+        <v>17.2</v>
       </c>
       <c r="C600" s="4" t="n">
-        <v>-0.0515</v>
+        <v>-0.0529</v>
       </c>
       <c r="D600" s="5" t="n">
-        <v>157580</v>
+        <v>41580000</v>
       </c>
       <c r="E600" s="2" t="inlineStr"/>
       <c r="F600" s="3" t="n">
-        <v>9.73</v>
+        <v>48.54</v>
       </c>
       <c r="G600" s="2" t="inlineStr"/>
       <c r="H600" s="2" t="inlineStr"/>
@@ -26398,86 +26396,90 @@
       <c r="J600" s="2" t="inlineStr"/>
       <c r="K600" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
-        </is>
-      </c>
-      <c r="L600" s="2" t="inlineStr"/>
+          <t>Ticari hizmetler</t>
+        </is>
+      </c>
+      <c r="L600" s="2" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST MALİ, BIST ANA, BIST TEMETTU</t>
+        </is>
+      </c>
       <c r="M600" s="2" t="inlineStr"/>
     </row>
     <row r="601">
       <c r="A601" s="6" t="inlineStr">
         <is>
-          <t>MMCAS</t>
+          <t>ARZUM</t>
         </is>
       </c>
       <c r="B601" s="7" t="n">
-        <v>68</v>
+        <v>2.41</v>
       </c>
       <c r="C601" s="8" t="n">
-        <v>-0.0159</v>
+        <v>-0.0282</v>
       </c>
       <c r="D601" s="9" t="n">
-        <v>46110</v>
+        <v>20190000</v>
       </c>
       <c r="E601" s="8" t="n">
-        <v>0.58</v>
+        <v>1</v>
       </c>
       <c r="F601" s="7" t="n">
-        <v>35.57</v>
+        <v>32.41</v>
       </c>
       <c r="G601" s="6" t="inlineStr"/>
       <c r="H601" s="6" t="inlineStr"/>
       <c r="I601" s="8" t="n">
-        <v>-9.409700000000001</v>
+        <v>-191.6342</v>
       </c>
       <c r="J601" s="8" t="n">
-        <v>-4.155</v>
+        <v>-0.8093</v>
       </c>
       <c r="K601" s="6" t="inlineStr">
         <is>
-          <t>Taşımacılık</t>
-        </is>
-      </c>
-      <c r="L601" s="6" t="inlineStr"/>
+          <t>Dağıtım servisleri</t>
+        </is>
+      </c>
+      <c r="L601" s="6" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST KURUMSAL YÖNETİM</t>
+        </is>
+      </c>
       <c r="M601" s="6" t="inlineStr"/>
     </row>
     <row r="602">
       <c r="A602" s="2" t="inlineStr">
         <is>
-          <t>BORLS</t>
+          <t>UCAYM</t>
         </is>
       </c>
       <c r="B602" s="3" t="n">
-        <v>6.27</v>
+        <v>30.14</v>
       </c>
       <c r="C602" s="4" t="n">
-        <v>0.0503</v>
+        <v>-0.0163</v>
       </c>
       <c r="D602" s="5" t="n">
-        <v>28590000</v>
+        <v>16090000</v>
       </c>
       <c r="E602" s="4" t="n">
-        <v>0.1672</v>
+        <v>0.2667</v>
       </c>
       <c r="F602" s="3" t="n">
-        <v>51.76</v>
+        <v>50.55</v>
       </c>
       <c r="G602" s="2" t="inlineStr"/>
       <c r="H602" s="2" t="inlineStr"/>
-      <c r="I602" s="4" t="n">
-        <v>-5.3262</v>
-      </c>
-      <c r="J602" s="4" t="n">
-        <v>-4.2562</v>
-      </c>
+      <c r="I602" s="2" t="inlineStr"/>
+      <c r="J602" s="2" t="inlineStr"/>
       <c r="K602" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Endüstriyel hizmetler</t>
         </is>
       </c>
       <c r="L602" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST YILDIZ</t>
+          <t>BIST TUM-100, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M602" s="2" t="inlineStr"/>
@@ -26485,21 +26487,21 @@
     <row r="603">
       <c r="A603" s="6" t="inlineStr">
         <is>
-          <t>MARMR</t>
+          <t>AAGYO</t>
         </is>
       </c>
       <c r="B603" s="7" t="n">
-        <v>2.79</v>
+        <v>18.35</v>
       </c>
       <c r="C603" s="8" t="n">
-        <v>0.022</v>
+        <v>-0.0097</v>
       </c>
       <c r="D603" s="9" t="n">
-        <v>136120000</v>
+        <v>54120000</v>
       </c>
       <c r="E603" s="6" t="inlineStr"/>
       <c r="F603" s="7" t="n">
-        <v>48.9</v>
+        <v>35.07</v>
       </c>
       <c r="G603" s="6" t="inlineStr"/>
       <c r="H603" s="6" t="inlineStr"/>
@@ -26512,7 +26514,7 @@
       </c>
       <c r="L603" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST KOCAELI</t>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M603" s="6" t="inlineStr"/>
@@ -26520,21 +26522,21 @@
     <row r="604">
       <c r="A604" s="2" t="inlineStr">
         <is>
-          <t>BESTE</t>
+          <t>CGCAM</t>
         </is>
       </c>
       <c r="B604" s="3" t="n">
-        <v>28.66</v>
+        <v>40.22</v>
       </c>
       <c r="C604" s="4" t="n">
-        <v>0.0092</v>
+        <v>-0.0496</v>
       </c>
       <c r="D604" s="5" t="n">
-        <v>21030000</v>
+        <v>5940000</v>
       </c>
       <c r="E604" s="2" t="inlineStr"/>
       <c r="F604" s="3" t="n">
-        <v>56.71</v>
+        <v>46.69</v>
       </c>
       <c r="G604" s="2" t="inlineStr"/>
       <c r="H604" s="2" t="inlineStr"/>
@@ -26542,12 +26544,12 @@
       <c r="J604" s="2" t="inlineStr"/>
       <c r="K604" s="2" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Dayanıklı tüketim malları</t>
         </is>
       </c>
       <c r="L604" s="2" t="inlineStr">
         <is>
-          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST HALKA ARZ, BIST ANA, BIST MANİSA</t>
         </is>
       </c>
       <c r="M604" s="2" t="inlineStr"/>
@@ -26555,21 +26557,21 @@
     <row r="605">
       <c r="A605" s="6" t="inlineStr">
         <is>
-          <t>MCARD</t>
+          <t>LXGYO</t>
         </is>
       </c>
       <c r="B605" s="7" t="n">
-        <v>186.3</v>
+        <v>16.41</v>
       </c>
       <c r="C605" s="8" t="n">
-        <v>-0.061</v>
-      </c>
-      <c r="D605" s="7" t="n">
-        <v>8119999.999999999</v>
+        <v>-0.0375</v>
+      </c>
+      <c r="D605" s="9" t="n">
+        <v>45440000</v>
       </c>
       <c r="E605" s="6" t="inlineStr"/>
       <c r="F605" s="7" t="n">
-        <v>55.08</v>
+        <v>45.93</v>
       </c>
       <c r="G605" s="6" t="inlineStr"/>
       <c r="H605" s="6" t="inlineStr"/>
@@ -26577,12 +26579,12 @@
       <c r="J605" s="6" t="inlineStr"/>
       <c r="K605" s="6" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L605" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEMETTU, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KATILIM TEMETTU</t>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M605" s="6" t="inlineStr"/>
@@ -26590,96 +26592,100 @@
     <row r="606">
       <c r="A606" s="2" t="inlineStr">
         <is>
-          <t>ALTIN</t>
+          <t>GENKM</t>
         </is>
       </c>
       <c r="B606" s="3" t="n">
-        <v>77.5</v>
+        <v>13.5</v>
       </c>
       <c r="C606" s="4" t="n">
-        <v>-0.0142</v>
+        <v>-0.033</v>
       </c>
       <c r="D606" s="5" t="n">
-        <v>11650000</v>
+        <v>28970000</v>
       </c>
       <c r="E606" s="2" t="inlineStr"/>
       <c r="F606" s="3" t="n">
-        <v>33.33</v>
+        <v>44.26</v>
       </c>
       <c r="G606" s="2" t="inlineStr"/>
       <c r="H606" s="2" t="inlineStr"/>
       <c r="I606" s="2" t="inlineStr"/>
       <c r="J606" s="2" t="inlineStr"/>
-      <c r="K606" s="2" t="inlineStr"/>
-      <c r="L606" s="2" t="inlineStr"/>
+      <c r="K606" s="2" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
+      <c r="L606" s="2" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST KOCAELI</t>
+        </is>
+      </c>
       <c r="M606" s="2" t="inlineStr"/>
     </row>
     <row r="607">
       <c r="A607" s="6" t="inlineStr">
         <is>
-          <t>LXGYO</t>
+          <t>ALTIN</t>
         </is>
       </c>
       <c r="B607" s="7" t="n">
-        <v>16.41</v>
+        <v>77.5</v>
       </c>
       <c r="C607" s="8" t="n">
-        <v>-0.0375</v>
+        <v>-0.0142</v>
       </c>
       <c r="D607" s="9" t="n">
-        <v>45440000</v>
+        <v>11650000</v>
       </c>
       <c r="E607" s="6" t="inlineStr"/>
       <c r="F607" s="7" t="n">
-        <v>45.93</v>
+        <v>33.33</v>
       </c>
       <c r="G607" s="6" t="inlineStr"/>
       <c r="H607" s="6" t="inlineStr"/>
       <c r="I607" s="6" t="inlineStr"/>
       <c r="J607" s="6" t="inlineStr"/>
-      <c r="K607" s="6" t="inlineStr">
-        <is>
-          <t>Finans</t>
-        </is>
-      </c>
-      <c r="L607" s="6" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST ANA</t>
-        </is>
-      </c>
+      <c r="K607" s="6" t="inlineStr"/>
+      <c r="L607" s="6" t="inlineStr"/>
       <c r="M607" s="6" t="inlineStr"/>
     </row>
     <row r="608">
       <c r="A608" s="2" t="inlineStr">
         <is>
-          <t>AAGYO</t>
+          <t>NETAS</t>
         </is>
       </c>
       <c r="B608" s="3" t="n">
-        <v>18.35</v>
+        <v>64.25</v>
       </c>
       <c r="C608" s="4" t="n">
-        <v>-0.0097</v>
+        <v>-0.0138</v>
       </c>
       <c r="D608" s="5" t="n">
-        <v>54120000</v>
-      </c>
-      <c r="E608" s="2" t="inlineStr"/>
+        <v>748500</v>
+      </c>
+      <c r="E608" s="4" t="n">
+        <v>0.3695000000000001</v>
+      </c>
       <c r="F608" s="3" t="n">
-        <v>35.07</v>
+        <v>47.67</v>
       </c>
       <c r="G608" s="2" t="inlineStr"/>
       <c r="H608" s="2" t="inlineStr"/>
       <c r="I608" s="2" t="inlineStr"/>
-      <c r="J608" s="2" t="inlineStr"/>
+      <c r="J608" s="4" t="n">
+        <v>0.1431</v>
+      </c>
       <c r="K608" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Teknoloji hizmetleri</t>
         </is>
       </c>
       <c r="L608" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST YILDIZ</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KURUMSAL YÖNETİM</t>
         </is>
       </c>
       <c r="M608" s="2" t="inlineStr"/>
@@ -26687,40 +26693,36 @@
     <row r="609">
       <c r="A609" s="6" t="inlineStr">
         <is>
-          <t>ARZUM</t>
+          <t>ICUGS</t>
         </is>
       </c>
       <c r="B609" s="7" t="n">
-        <v>2.41</v>
+        <v>6.35</v>
       </c>
       <c r="C609" s="8" t="n">
-        <v>-0.0282</v>
+        <v>-0.014</v>
       </c>
       <c r="D609" s="9" t="n">
-        <v>20190000</v>
+        <v>13400000</v>
       </c>
       <c r="E609" s="8" t="n">
-        <v>1</v>
+        <v>0.8667</v>
       </c>
       <c r="F609" s="7" t="n">
-        <v>32.41</v>
+        <v>68.08</v>
       </c>
       <c r="G609" s="6" t="inlineStr"/>
       <c r="H609" s="6" t="inlineStr"/>
-      <c r="I609" s="8" t="n">
-        <v>-191.6342</v>
-      </c>
-      <c r="J609" s="8" t="n">
-        <v>-0.8093</v>
-      </c>
+      <c r="I609" s="6" t="inlineStr"/>
+      <c r="J609" s="6" t="inlineStr"/>
       <c r="K609" s="6" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L609" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST KURUMSAL YÖNETİM</t>
+          <t>BIST TUM-100, BIST TÜM, BIST MALİ, BIST ANA</t>
         </is>
       </c>
       <c r="M609" s="6" t="inlineStr"/>
@@ -26728,34 +26730,40 @@
     <row r="610">
       <c r="A610" s="2" t="inlineStr">
         <is>
-          <t>FRMPL</t>
+          <t>BORLS</t>
         </is>
       </c>
       <c r="B610" s="3" t="n">
-        <v>40.04</v>
+        <v>6.27</v>
       </c>
       <c r="C610" s="4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D610" s="3" t="n">
-        <v>8289999.999999999</v>
-      </c>
-      <c r="E610" s="2" t="inlineStr"/>
+        <v>0.0503</v>
+      </c>
+      <c r="D610" s="5" t="n">
+        <v>28590000</v>
+      </c>
+      <c r="E610" s="4" t="n">
+        <v>0.1672</v>
+      </c>
       <c r="F610" s="3" t="n">
-        <v>68.78</v>
+        <v>51.76</v>
       </c>
       <c r="G610" s="2" t="inlineStr"/>
       <c r="H610" s="2" t="inlineStr"/>
-      <c r="I610" s="2" t="inlineStr"/>
-      <c r="J610" s="2" t="inlineStr"/>
+      <c r="I610" s="4" t="n">
+        <v>-5.3262</v>
+      </c>
+      <c r="J610" s="4" t="n">
+        <v>-4.2562</v>
+      </c>
       <c r="K610" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L610" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST TEKİRDAĞ</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M610" s="2" t="inlineStr"/>
@@ -26763,42 +26771,32 @@
     <row r="611">
       <c r="A611" s="6" t="inlineStr">
         <is>
-          <t>CRFSA</t>
+          <t>ENPRA</t>
         </is>
       </c>
       <c r="B611" s="7" t="n">
-        <v>136.9</v>
+        <v>70</v>
       </c>
       <c r="C611" s="8" t="n">
-        <v>-0.0406</v>
+        <v>-0.0515</v>
       </c>
       <c r="D611" s="9" t="n">
-        <v>919670</v>
-      </c>
-      <c r="E611" s="8" t="n">
-        <v>0.1071</v>
-      </c>
+        <v>157580</v>
+      </c>
+      <c r="E611" s="6" t="inlineStr"/>
       <c r="F611" s="7" t="n">
-        <v>44.13</v>
+        <v>9.73</v>
       </c>
       <c r="G611" s="6" t="inlineStr"/>
       <c r="H611" s="6" t="inlineStr"/>
-      <c r="I611" s="8" t="n">
-        <v>-3.6635</v>
-      </c>
-      <c r="J611" s="8" t="n">
-        <v>-0.4897</v>
-      </c>
+      <c r="I611" s="6" t="inlineStr"/>
+      <c r="J611" s="6" t="inlineStr"/>
       <c r="K611" s="6" t="inlineStr">
         <is>
-          <t>Perakende satış</t>
-        </is>
-      </c>
-      <c r="L611" s="6" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST ANA</t>
-        </is>
-      </c>
+          <t>Finans</t>
+        </is>
+      </c>
+      <c r="L611" s="6" t="inlineStr"/>
       <c r="M611" s="6" t="inlineStr"/>
     </row>
   </sheetData>
@@ -26823,7 +26821,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>20.05.2026 15:30</t>
+          <t>20.05.2026 16:30</t>
         </is>
       </c>
     </row>

--- a/data/bist_screener_2026-05-20.xlsx
+++ b/data/bist_screener_2026-05-20.xlsx
@@ -25903,54 +25903,66 @@
     <row r="587">
       <c r="A587" s="6" t="inlineStr">
         <is>
-          <t>INTEK</t>
+          <t>LILAK</t>
         </is>
       </c>
       <c r="B587" s="7" t="n">
-        <v>234</v>
+        <v>33.9</v>
       </c>
       <c r="C587" s="8" t="n">
-        <v>-0.0254</v>
+        <v>-0.0225</v>
       </c>
       <c r="D587" s="9" t="n">
-        <v>10360</v>
+        <v>4990000</v>
       </c>
       <c r="E587" s="8" t="n">
-        <v>0.2578</v>
+        <v>0.3528</v>
       </c>
       <c r="F587" s="7" t="n">
-        <v>39.91</v>
-      </c>
-      <c r="G587" s="6" t="inlineStr"/>
+        <v>40.78</v>
+      </c>
+      <c r="G587" s="7" t="n">
+        <v>13.4</v>
+      </c>
       <c r="H587" s="6" t="inlineStr"/>
-      <c r="I587" s="6" t="inlineStr"/>
-      <c r="J587" s="6" t="inlineStr"/>
+      <c r="I587" s="8" t="n">
+        <v>0.1029</v>
+      </c>
+      <c r="J587" s="8" t="n">
+        <v>-1.4864</v>
+      </c>
       <c r="K587" s="6" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
-        </is>
-      </c>
-      <c r="L587" s="6" t="inlineStr"/>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
+      <c r="L587" s="6" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST HALKA ARZ, BIST ORMAN KAĞIT BASIM, BIST YILDIZ, BIST TEMETTU, BIST KURUMSAL YÖNETİM, BIST TEKİRDAĞ</t>
+        </is>
+      </c>
       <c r="M587" s="6" t="inlineStr"/>
     </row>
     <row r="588">
       <c r="A588" s="2" t="inlineStr">
         <is>
-          <t>EMPAE</t>
+          <t>INTEK</t>
         </is>
       </c>
       <c r="B588" s="3" t="n">
-        <v>79.59999999999999</v>
+        <v>234</v>
       </c>
       <c r="C588" s="4" t="n">
-        <v>0.0304</v>
+        <v>-0.0254</v>
       </c>
       <c r="D588" s="5" t="n">
-        <v>29700000</v>
-      </c>
-      <c r="E588" s="2" t="inlineStr"/>
+        <v>10360</v>
+      </c>
+      <c r="E588" s="4" t="n">
+        <v>0.2578</v>
+      </c>
       <c r="F588" s="3" t="n">
-        <v>89.59</v>
+        <v>39.91</v>
       </c>
       <c r="G588" s="2" t="inlineStr"/>
       <c r="H588" s="2" t="inlineStr"/>
@@ -25958,55 +25970,43 @@
       <c r="J588" s="2" t="inlineStr"/>
       <c r="K588" s="2" t="inlineStr">
         <is>
-          <t>Elektronik teknoloji</t>
-        </is>
-      </c>
-      <c r="L588" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEMETTU, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KATILIM TEMETTU</t>
-        </is>
-      </c>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
+      <c r="L588" s="2" t="inlineStr"/>
       <c r="M588" s="2" t="inlineStr"/>
     </row>
     <row r="589">
       <c r="A589" s="6" t="inlineStr">
         <is>
-          <t>LILAK</t>
+          <t>AAGYO</t>
         </is>
       </c>
       <c r="B589" s="7" t="n">
-        <v>33.9</v>
+        <v>18.35</v>
       </c>
       <c r="C589" s="8" t="n">
-        <v>-0.0225</v>
+        <v>-0.0097</v>
       </c>
       <c r="D589" s="9" t="n">
-        <v>4990000</v>
-      </c>
-      <c r="E589" s="8" t="n">
-        <v>0.3528</v>
-      </c>
+        <v>54120000</v>
+      </c>
+      <c r="E589" s="6" t="inlineStr"/>
       <c r="F589" s="7" t="n">
-        <v>40.78</v>
-      </c>
-      <c r="G589" s="7" t="n">
-        <v>13.4</v>
-      </c>
+        <v>35.07</v>
+      </c>
+      <c r="G589" s="6" t="inlineStr"/>
       <c r="H589" s="6" t="inlineStr"/>
-      <c r="I589" s="8" t="n">
-        <v>0.1029</v>
-      </c>
-      <c r="J589" s="8" t="n">
-        <v>-1.4864</v>
-      </c>
+      <c r="I589" s="6" t="inlineStr"/>
+      <c r="J589" s="6" t="inlineStr"/>
       <c r="K589" s="6" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L589" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST HALKA ARZ, BIST ORMAN KAĞIT BASIM, BIST YILDIZ, BIST TEMETTU, BIST KURUMSAL YÖNETİM, BIST TEKİRDAĞ</t>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M589" s="6" t="inlineStr"/>
@@ -26014,40 +26014,34 @@
     <row r="590">
       <c r="A590" s="2" t="inlineStr">
         <is>
-          <t>CRFSA</t>
+          <t>CGCAM</t>
         </is>
       </c>
       <c r="B590" s="3" t="n">
-        <v>136.9</v>
+        <v>40.22</v>
       </c>
       <c r="C590" s="4" t="n">
-        <v>-0.0406</v>
+        <v>-0.0496</v>
       </c>
       <c r="D590" s="5" t="n">
-        <v>919670</v>
-      </c>
-      <c r="E590" s="4" t="n">
-        <v>0.1071</v>
-      </c>
+        <v>5940000</v>
+      </c>
+      <c r="E590" s="2" t="inlineStr"/>
       <c r="F590" s="3" t="n">
-        <v>44.13</v>
+        <v>46.69</v>
       </c>
       <c r="G590" s="2" t="inlineStr"/>
       <c r="H590" s="2" t="inlineStr"/>
-      <c r="I590" s="4" t="n">
-        <v>-3.6635</v>
-      </c>
-      <c r="J590" s="4" t="n">
-        <v>-0.4897</v>
-      </c>
+      <c r="I590" s="2" t="inlineStr"/>
+      <c r="J590" s="2" t="inlineStr"/>
       <c r="K590" s="2" t="inlineStr">
         <is>
-          <t>Perakende satış</t>
+          <t>Dayanıklı tüketim malları</t>
         </is>
       </c>
       <c r="L590" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST ANA</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST HALKA ARZ, BIST ANA, BIST MANİSA</t>
         </is>
       </c>
       <c r="M590" s="2" t="inlineStr"/>
@@ -26055,58 +26049,58 @@
     <row r="591">
       <c r="A591" s="6" t="inlineStr">
         <is>
-          <t>BRMEN</t>
+          <t>ICUGS</t>
         </is>
       </c>
       <c r="B591" s="7" t="n">
-        <v>10.58</v>
+        <v>6.35</v>
       </c>
       <c r="C591" s="8" t="n">
-        <v>0.0655</v>
+        <v>-0.014</v>
       </c>
       <c r="D591" s="9" t="n">
-        <v>722290</v>
+        <v>13400000</v>
       </c>
       <c r="E591" s="8" t="n">
-        <v>0.95</v>
+        <v>0.8667</v>
       </c>
       <c r="F591" s="7" t="n">
-        <v>64.97</v>
+        <v>68.08</v>
       </c>
       <c r="G591" s="6" t="inlineStr"/>
       <c r="H591" s="6" t="inlineStr"/>
-      <c r="I591" s="8" t="n">
-        <v>-23.6291</v>
-      </c>
-      <c r="J591" s="8" t="n">
-        <v>-0.4678</v>
-      </c>
+      <c r="I591" s="6" t="inlineStr"/>
+      <c r="J591" s="6" t="inlineStr"/>
       <c r="K591" s="6" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
-        </is>
-      </c>
-      <c r="L591" s="6" t="inlineStr"/>
+          <t>Finans</t>
+        </is>
+      </c>
+      <c r="L591" s="6" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST MALİ, BIST ANA</t>
+        </is>
+      </c>
       <c r="M591" s="6" t="inlineStr"/>
     </row>
     <row r="592">
       <c r="A592" s="2" t="inlineStr">
         <is>
-          <t>MCARD</t>
+          <t>MARMR</t>
         </is>
       </c>
       <c r="B592" s="3" t="n">
-        <v>186.3</v>
+        <v>2.79</v>
       </c>
       <c r="C592" s="4" t="n">
-        <v>-0.061</v>
-      </c>
-      <c r="D592" s="3" t="n">
-        <v>8119999.999999999</v>
+        <v>0.022</v>
+      </c>
+      <c r="D592" s="5" t="n">
+        <v>136120000</v>
       </c>
       <c r="E592" s="2" t="inlineStr"/>
       <c r="F592" s="3" t="n">
-        <v>55.08</v>
+        <v>48.9</v>
       </c>
       <c r="G592" s="2" t="inlineStr"/>
       <c r="H592" s="2" t="inlineStr"/>
@@ -26114,12 +26108,12 @@
       <c r="J592" s="2" t="inlineStr"/>
       <c r="K592" s="2" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L592" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEMETTU, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KATILIM TEMETTU</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST KOCAELI</t>
         </is>
       </c>
       <c r="M592" s="2" t="inlineStr"/>
@@ -26127,21 +26121,23 @@
     <row r="593">
       <c r="A593" s="6" t="inlineStr">
         <is>
-          <t>BESTE</t>
+          <t>UCAYM</t>
         </is>
       </c>
       <c r="B593" s="7" t="n">
-        <v>28.66</v>
+        <v>30.14</v>
       </c>
       <c r="C593" s="8" t="n">
-        <v>0.0092</v>
+        <v>-0.0163</v>
       </c>
       <c r="D593" s="9" t="n">
-        <v>21030000</v>
-      </c>
-      <c r="E593" s="6" t="inlineStr"/>
+        <v>16090000</v>
+      </c>
+      <c r="E593" s="8" t="n">
+        <v>0.2667</v>
+      </c>
       <c r="F593" s="7" t="n">
-        <v>56.71</v>
+        <v>50.55</v>
       </c>
       <c r="G593" s="6" t="inlineStr"/>
       <c r="H593" s="6" t="inlineStr"/>
@@ -26149,12 +26145,12 @@
       <c r="J593" s="6" t="inlineStr"/>
       <c r="K593" s="6" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Endüstriyel hizmetler</t>
         </is>
       </c>
       <c r="L593" s="6" t="inlineStr">
         <is>
-          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M593" s="6" t="inlineStr"/>
@@ -26162,21 +26158,21 @@
     <row r="594">
       <c r="A594" s="2" t="inlineStr">
         <is>
-          <t>MARMR</t>
+          <t>DMLKT</t>
         </is>
       </c>
       <c r="B594" s="3" t="n">
-        <v>2.79</v>
+        <v>6.01</v>
       </c>
       <c r="C594" s="4" t="n">
-        <v>0.022</v>
+        <v>-0.0083</v>
       </c>
       <c r="D594" s="5" t="n">
-        <v>136120000</v>
+        <v>7810000</v>
       </c>
       <c r="E594" s="2" t="inlineStr"/>
       <c r="F594" s="3" t="n">
-        <v>48.9</v>
+        <v>39.62</v>
       </c>
       <c r="G594" s="2" t="inlineStr"/>
       <c r="H594" s="2" t="inlineStr"/>
@@ -26187,31 +26183,27 @@
           <t>Finans</t>
         </is>
       </c>
-      <c r="L594" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST KOCAELI</t>
-        </is>
-      </c>
+      <c r="L594" s="2" t="inlineStr"/>
       <c r="M594" s="2" t="inlineStr"/>
     </row>
     <row r="595">
       <c r="A595" s="6" t="inlineStr">
         <is>
-          <t>DMLKT</t>
+          <t>EMPAE</t>
         </is>
       </c>
       <c r="B595" s="7" t="n">
-        <v>6.01</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="C595" s="8" t="n">
-        <v>-0.0083</v>
+        <v>0.0304</v>
       </c>
       <c r="D595" s="9" t="n">
-        <v>7810000</v>
+        <v>29700000</v>
       </c>
       <c r="E595" s="6" t="inlineStr"/>
       <c r="F595" s="7" t="n">
-        <v>39.62</v>
+        <v>89.59</v>
       </c>
       <c r="G595" s="6" t="inlineStr"/>
       <c r="H595" s="6" t="inlineStr"/>
@@ -26219,47 +26211,47 @@
       <c r="J595" s="6" t="inlineStr"/>
       <c r="K595" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
-        </is>
-      </c>
-      <c r="L595" s="6" t="inlineStr"/>
+          <t>Elektronik teknoloji</t>
+        </is>
+      </c>
+      <c r="L595" s="6" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEMETTU, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KATILIM TEMETTU</t>
+        </is>
+      </c>
       <c r="M595" s="6" t="inlineStr"/>
     </row>
     <row r="596">
       <c r="A596" s="2" t="inlineStr">
         <is>
-          <t>VKING</t>
+          <t>GLRMK</t>
         </is>
       </c>
       <c r="B596" s="3" t="n">
-        <v>25.2</v>
+        <v>177.4</v>
       </c>
       <c r="C596" s="4" t="n">
-        <v>-0.0315</v>
+        <v>-0.0067</v>
       </c>
       <c r="D596" s="5" t="n">
-        <v>857620</v>
-      </c>
-      <c r="E596" s="4" t="n">
-        <v>0.9698</v>
-      </c>
+        <v>7980000</v>
+      </c>
+      <c r="E596" s="2" t="inlineStr"/>
       <c r="F596" s="3" t="n">
-        <v>38.25</v>
+        <v>38.18</v>
       </c>
       <c r="G596" s="2" t="inlineStr"/>
       <c r="H596" s="2" t="inlineStr"/>
       <c r="I596" s="2" t="inlineStr"/>
-      <c r="J596" s="4" t="n">
-        <v>0.6453</v>
-      </c>
+      <c r="J596" s="2" t="inlineStr"/>
       <c r="K596" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Endüstriyel hizmetler</t>
         </is>
       </c>
       <c r="L596" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST ORMAN KAĞIT BASIM, BIST ANA, BIST İZMİR</t>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST ANKARA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
         </is>
       </c>
       <c r="M596" s="2" t="inlineStr"/>
@@ -26267,128 +26259,122 @@
     <row r="597">
       <c r="A597" s="6" t="inlineStr">
         <is>
-          <t>MMCAS</t>
+          <t>ALTIN</t>
         </is>
       </c>
       <c r="B597" s="7" t="n">
-        <v>68</v>
+        <v>77.5</v>
       </c>
       <c r="C597" s="8" t="n">
-        <v>-0.0159</v>
+        <v>-0.0142</v>
       </c>
       <c r="D597" s="9" t="n">
-        <v>46110</v>
-      </c>
-      <c r="E597" s="8" t="n">
-        <v>0.58</v>
-      </c>
+        <v>11650000</v>
+      </c>
+      <c r="E597" s="6" t="inlineStr"/>
       <c r="F597" s="7" t="n">
-        <v>35.57</v>
+        <v>33.33</v>
       </c>
       <c r="G597" s="6" t="inlineStr"/>
       <c r="H597" s="6" t="inlineStr"/>
-      <c r="I597" s="8" t="n">
-        <v>-9.409700000000001</v>
-      </c>
-      <c r="J597" s="8" t="n">
-        <v>-4.155</v>
-      </c>
-      <c r="K597" s="6" t="inlineStr">
-        <is>
-          <t>Taşımacılık</t>
-        </is>
-      </c>
+      <c r="I597" s="6" t="inlineStr"/>
+      <c r="J597" s="6" t="inlineStr"/>
+      <c r="K597" s="6" t="inlineStr"/>
       <c r="L597" s="6" t="inlineStr"/>
       <c r="M597" s="6" t="inlineStr"/>
     </row>
     <row r="598">
       <c r="A598" s="2" t="inlineStr">
         <is>
-          <t>FRMPL</t>
+          <t>BRMEN</t>
         </is>
       </c>
       <c r="B598" s="3" t="n">
-        <v>40.04</v>
+        <v>10.58</v>
       </c>
       <c r="C598" s="4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D598" s="3" t="n">
-        <v>8289999.999999999</v>
-      </c>
-      <c r="E598" s="2" t="inlineStr"/>
+        <v>0.0655</v>
+      </c>
+      <c r="D598" s="5" t="n">
+        <v>722290</v>
+      </c>
+      <c r="E598" s="4" t="n">
+        <v>0.95</v>
+      </c>
       <c r="F598" s="3" t="n">
-        <v>68.78</v>
+        <v>64.97</v>
       </c>
       <c r="G598" s="2" t="inlineStr"/>
       <c r="H598" s="2" t="inlineStr"/>
-      <c r="I598" s="2" t="inlineStr"/>
-      <c r="J598" s="2" t="inlineStr"/>
+      <c r="I598" s="4" t="n">
+        <v>-23.6291</v>
+      </c>
+      <c r="J598" s="4" t="n">
+        <v>-0.4678</v>
+      </c>
       <c r="K598" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
-        </is>
-      </c>
-      <c r="L598" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST TEKİRDAĞ</t>
-        </is>
-      </c>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
+      <c r="L598" s="2" t="inlineStr"/>
       <c r="M598" s="2" t="inlineStr"/>
     </row>
     <row r="599">
       <c r="A599" s="6" t="inlineStr">
         <is>
-          <t>GLRMK</t>
+          <t>MMCAS</t>
         </is>
       </c>
       <c r="B599" s="7" t="n">
-        <v>177.4</v>
+        <v>68</v>
       </c>
       <c r="C599" s="8" t="n">
-        <v>-0.0067</v>
+        <v>-0.0159</v>
       </c>
       <c r="D599" s="9" t="n">
-        <v>7980000</v>
-      </c>
-      <c r="E599" s="6" t="inlineStr"/>
+        <v>46110</v>
+      </c>
+      <c r="E599" s="8" t="n">
+        <v>0.58</v>
+      </c>
       <c r="F599" s="7" t="n">
-        <v>38.18</v>
+        <v>35.57</v>
       </c>
       <c r="G599" s="6" t="inlineStr"/>
       <c r="H599" s="6" t="inlineStr"/>
-      <c r="I599" s="6" t="inlineStr"/>
-      <c r="J599" s="6" t="inlineStr"/>
+      <c r="I599" s="8" t="n">
+        <v>-9.409700000000001</v>
+      </c>
+      <c r="J599" s="8" t="n">
+        <v>-4.155</v>
+      </c>
       <c r="K599" s="6" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
-        </is>
-      </c>
-      <c r="L599" s="6" t="inlineStr">
-        <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST ANKARA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
-        </is>
-      </c>
+          <t>Taşımacılık</t>
+        </is>
+      </c>
+      <c r="L599" s="6" t="inlineStr"/>
       <c r="M599" s="6" t="inlineStr"/>
     </row>
     <row r="600">
       <c r="A600" s="2" t="inlineStr">
         <is>
-          <t>SMRVA</t>
+          <t>LXGYO</t>
         </is>
       </c>
       <c r="B600" s="3" t="n">
-        <v>17.2</v>
+        <v>16.41</v>
       </c>
       <c r="C600" s="4" t="n">
-        <v>-0.0529</v>
+        <v>-0.0375</v>
       </c>
       <c r="D600" s="5" t="n">
-        <v>41580000</v>
+        <v>45440000</v>
       </c>
       <c r="E600" s="2" t="inlineStr"/>
       <c r="F600" s="3" t="n">
-        <v>48.54</v>
+        <v>45.93</v>
       </c>
       <c r="G600" s="2" t="inlineStr"/>
       <c r="H600" s="2" t="inlineStr"/>
@@ -26396,12 +26382,12 @@
       <c r="J600" s="2" t="inlineStr"/>
       <c r="K600" s="2" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L600" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST MALİ, BIST ANA, BIST TEMETTU</t>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M600" s="2" t="inlineStr"/>
@@ -26409,40 +26395,38 @@
     <row r="601">
       <c r="A601" s="6" t="inlineStr">
         <is>
-          <t>ARZUM</t>
+          <t>VKING</t>
         </is>
       </c>
       <c r="B601" s="7" t="n">
-        <v>2.41</v>
+        <v>25.2</v>
       </c>
       <c r="C601" s="8" t="n">
-        <v>-0.0282</v>
+        <v>-0.0315</v>
       </c>
       <c r="D601" s="9" t="n">
-        <v>20190000</v>
+        <v>857620</v>
       </c>
       <c r="E601" s="8" t="n">
-        <v>1</v>
+        <v>0.9698</v>
       </c>
       <c r="F601" s="7" t="n">
-        <v>32.41</v>
+        <v>38.25</v>
       </c>
       <c r="G601" s="6" t="inlineStr"/>
       <c r="H601" s="6" t="inlineStr"/>
-      <c r="I601" s="8" t="n">
-        <v>-191.6342</v>
-      </c>
+      <c r="I601" s="6" t="inlineStr"/>
       <c r="J601" s="8" t="n">
-        <v>-0.8093</v>
+        <v>0.6453</v>
       </c>
       <c r="K601" s="6" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="L601" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST KURUMSAL YÖNETİM</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST ORMAN KAĞIT BASIM, BIST ANA, BIST İZMİR</t>
         </is>
       </c>
       <c r="M601" s="6" t="inlineStr"/>
@@ -26450,36 +26434,40 @@
     <row r="602">
       <c r="A602" s="2" t="inlineStr">
         <is>
-          <t>UCAYM</t>
+          <t>BORLS</t>
         </is>
       </c>
       <c r="B602" s="3" t="n">
-        <v>30.14</v>
+        <v>6.27</v>
       </c>
       <c r="C602" s="4" t="n">
-        <v>-0.0163</v>
+        <v>0.0503</v>
       </c>
       <c r="D602" s="5" t="n">
-        <v>16090000</v>
+        <v>28590000</v>
       </c>
       <c r="E602" s="4" t="n">
-        <v>0.2667</v>
+        <v>0.1672</v>
       </c>
       <c r="F602" s="3" t="n">
-        <v>50.55</v>
+        <v>51.76</v>
       </c>
       <c r="G602" s="2" t="inlineStr"/>
       <c r="H602" s="2" t="inlineStr"/>
-      <c r="I602" s="2" t="inlineStr"/>
-      <c r="J602" s="2" t="inlineStr"/>
+      <c r="I602" s="4" t="n">
+        <v>-5.3262</v>
+      </c>
+      <c r="J602" s="4" t="n">
+        <v>-4.2562</v>
+      </c>
       <c r="K602" s="2" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L602" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M602" s="2" t="inlineStr"/>
@@ -26487,34 +26475,40 @@
     <row r="603">
       <c r="A603" s="6" t="inlineStr">
         <is>
-          <t>AAGYO</t>
+          <t>CRFSA</t>
         </is>
       </c>
       <c r="B603" s="7" t="n">
-        <v>18.35</v>
+        <v>136.9</v>
       </c>
       <c r="C603" s="8" t="n">
-        <v>-0.0097</v>
+        <v>-0.0406</v>
       </c>
       <c r="D603" s="9" t="n">
-        <v>54120000</v>
-      </c>
-      <c r="E603" s="6" t="inlineStr"/>
+        <v>919670</v>
+      </c>
+      <c r="E603" s="8" t="n">
+        <v>0.1071</v>
+      </c>
       <c r="F603" s="7" t="n">
-        <v>35.07</v>
+        <v>44.13</v>
       </c>
       <c r="G603" s="6" t="inlineStr"/>
       <c r="H603" s="6" t="inlineStr"/>
-      <c r="I603" s="6" t="inlineStr"/>
-      <c r="J603" s="6" t="inlineStr"/>
+      <c r="I603" s="8" t="n">
+        <v>-3.6635</v>
+      </c>
+      <c r="J603" s="8" t="n">
+        <v>-0.4897</v>
+      </c>
       <c r="K603" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Perakende satış</t>
         </is>
       </c>
       <c r="L603" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST YILDIZ</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST ANA</t>
         </is>
       </c>
       <c r="M603" s="6" t="inlineStr"/>
@@ -26522,21 +26516,21 @@
     <row r="604">
       <c r="A604" s="2" t="inlineStr">
         <is>
-          <t>CGCAM</t>
+          <t>ENPRA</t>
         </is>
       </c>
       <c r="B604" s="3" t="n">
-        <v>40.22</v>
+        <v>70</v>
       </c>
       <c r="C604" s="4" t="n">
-        <v>-0.0496</v>
+        <v>-0.0515</v>
       </c>
       <c r="D604" s="5" t="n">
-        <v>5940000</v>
+        <v>157580</v>
       </c>
       <c r="E604" s="2" t="inlineStr"/>
       <c r="F604" s="3" t="n">
-        <v>46.69</v>
+        <v>9.73</v>
       </c>
       <c r="G604" s="2" t="inlineStr"/>
       <c r="H604" s="2" t="inlineStr"/>
@@ -26544,47 +26538,47 @@
       <c r="J604" s="2" t="inlineStr"/>
       <c r="K604" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı tüketim malları</t>
-        </is>
-      </c>
-      <c r="L604" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST HALKA ARZ, BIST ANA, BIST MANİSA</t>
-        </is>
-      </c>
+          <t>Finans</t>
+        </is>
+      </c>
+      <c r="L604" s="2" t="inlineStr"/>
       <c r="M604" s="2" t="inlineStr"/>
     </row>
     <row r="605">
       <c r="A605" s="6" t="inlineStr">
         <is>
-          <t>LXGYO</t>
+          <t>NETAS</t>
         </is>
       </c>
       <c r="B605" s="7" t="n">
-        <v>16.41</v>
+        <v>64.25</v>
       </c>
       <c r="C605" s="8" t="n">
-        <v>-0.0375</v>
+        <v>-0.0138</v>
       </c>
       <c r="D605" s="9" t="n">
-        <v>45440000</v>
-      </c>
-      <c r="E605" s="6" t="inlineStr"/>
+        <v>748500</v>
+      </c>
+      <c r="E605" s="8" t="n">
+        <v>0.3695000000000001</v>
+      </c>
       <c r="F605" s="7" t="n">
-        <v>45.93</v>
+        <v>47.67</v>
       </c>
       <c r="G605" s="6" t="inlineStr"/>
       <c r="H605" s="6" t="inlineStr"/>
       <c r="I605" s="6" t="inlineStr"/>
-      <c r="J605" s="6" t="inlineStr"/>
+      <c r="J605" s="8" t="n">
+        <v>0.1431</v>
+      </c>
       <c r="K605" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Teknoloji hizmetleri</t>
         </is>
       </c>
       <c r="L605" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KURUMSAL YÖNETİM</t>
         </is>
       </c>
       <c r="M605" s="6" t="inlineStr"/>
@@ -26592,21 +26586,21 @@
     <row r="606">
       <c r="A606" s="2" t="inlineStr">
         <is>
-          <t>GENKM</t>
+          <t>MCARD</t>
         </is>
       </c>
       <c r="B606" s="3" t="n">
-        <v>13.5</v>
+        <v>186.3</v>
       </c>
       <c r="C606" s="4" t="n">
-        <v>-0.033</v>
-      </c>
-      <c r="D606" s="5" t="n">
-        <v>28970000</v>
+        <v>-0.061</v>
+      </c>
+      <c r="D606" s="3" t="n">
+        <v>8119999.999999999</v>
       </c>
       <c r="E606" s="2" t="inlineStr"/>
       <c r="F606" s="3" t="n">
-        <v>44.26</v>
+        <v>55.08</v>
       </c>
       <c r="G606" s="2" t="inlineStr"/>
       <c r="H606" s="2" t="inlineStr"/>
@@ -26614,12 +26608,12 @@
       <c r="J606" s="2" t="inlineStr"/>
       <c r="K606" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Ticari hizmetler</t>
         </is>
       </c>
       <c r="L606" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST KOCAELI</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEMETTU, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KATILIM TEMETTU</t>
         </is>
       </c>
       <c r="M606" s="2" t="inlineStr"/>
@@ -26627,65 +26621,69 @@
     <row r="607">
       <c r="A607" s="6" t="inlineStr">
         <is>
-          <t>ALTIN</t>
+          <t>GENKM</t>
         </is>
       </c>
       <c r="B607" s="7" t="n">
-        <v>77.5</v>
+        <v>13.5</v>
       </c>
       <c r="C607" s="8" t="n">
-        <v>-0.0142</v>
+        <v>-0.033</v>
       </c>
       <c r="D607" s="9" t="n">
-        <v>11650000</v>
+        <v>28970000</v>
       </c>
       <c r="E607" s="6" t="inlineStr"/>
       <c r="F607" s="7" t="n">
-        <v>33.33</v>
+        <v>44.26</v>
       </c>
       <c r="G607" s="6" t="inlineStr"/>
       <c r="H607" s="6" t="inlineStr"/>
       <c r="I607" s="6" t="inlineStr"/>
       <c r="J607" s="6" t="inlineStr"/>
-      <c r="K607" s="6" t="inlineStr"/>
-      <c r="L607" s="6" t="inlineStr"/>
+      <c r="K607" s="6" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
+      <c r="L607" s="6" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST KOCAELI</t>
+        </is>
+      </c>
       <c r="M607" s="6" t="inlineStr"/>
     </row>
     <row r="608">
       <c r="A608" s="2" t="inlineStr">
         <is>
-          <t>NETAS</t>
+          <t>SMRVA</t>
         </is>
       </c>
       <c r="B608" s="3" t="n">
-        <v>64.25</v>
+        <v>17.2</v>
       </c>
       <c r="C608" s="4" t="n">
-        <v>-0.0138</v>
+        <v>-0.0529</v>
       </c>
       <c r="D608" s="5" t="n">
-        <v>748500</v>
-      </c>
-      <c r="E608" s="4" t="n">
-        <v>0.3695000000000001</v>
-      </c>
+        <v>41580000</v>
+      </c>
+      <c r="E608" s="2" t="inlineStr"/>
       <c r="F608" s="3" t="n">
-        <v>47.67</v>
+        <v>48.54</v>
       </c>
       <c r="G608" s="2" t="inlineStr"/>
       <c r="H608" s="2" t="inlineStr"/>
       <c r="I608" s="2" t="inlineStr"/>
-      <c r="J608" s="4" t="n">
-        <v>0.1431</v>
-      </c>
+      <c r="J608" s="2" t="inlineStr"/>
       <c r="K608" s="2" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
+          <t>Ticari hizmetler</t>
         </is>
       </c>
       <c r="L608" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KURUMSAL YÖNETİM</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST MALİ, BIST ANA, BIST TEMETTU</t>
         </is>
       </c>
       <c r="M608" s="2" t="inlineStr"/>
@@ -26693,23 +26691,21 @@
     <row r="609">
       <c r="A609" s="6" t="inlineStr">
         <is>
-          <t>ICUGS</t>
+          <t>FRMPL</t>
         </is>
       </c>
       <c r="B609" s="7" t="n">
-        <v>6.35</v>
+        <v>40.04</v>
       </c>
       <c r="C609" s="8" t="n">
-        <v>-0.014</v>
-      </c>
-      <c r="D609" s="9" t="n">
-        <v>13400000</v>
-      </c>
-      <c r="E609" s="8" t="n">
-        <v>0.8667</v>
-      </c>
+        <v>0.1</v>
+      </c>
+      <c r="D609" s="7" t="n">
+        <v>8289999.999999999</v>
+      </c>
+      <c r="E609" s="6" t="inlineStr"/>
       <c r="F609" s="7" t="n">
-        <v>68.08</v>
+        <v>68.78</v>
       </c>
       <c r="G609" s="6" t="inlineStr"/>
       <c r="H609" s="6" t="inlineStr"/>
@@ -26717,12 +26713,12 @@
       <c r="J609" s="6" t="inlineStr"/>
       <c r="K609" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="L609" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST MALİ, BIST ANA</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST TEKİRDAĞ</t>
         </is>
       </c>
       <c r="M609" s="6" t="inlineStr"/>
@@ -26730,40 +26726,34 @@
     <row r="610">
       <c r="A610" s="2" t="inlineStr">
         <is>
-          <t>BORLS</t>
+          <t>BESTE</t>
         </is>
       </c>
       <c r="B610" s="3" t="n">
-        <v>6.27</v>
+        <v>28.66</v>
       </c>
       <c r="C610" s="4" t="n">
-        <v>0.0503</v>
+        <v>0.0092</v>
       </c>
       <c r="D610" s="5" t="n">
-        <v>28590000</v>
-      </c>
-      <c r="E610" s="4" t="n">
-        <v>0.1672</v>
-      </c>
+        <v>21030000</v>
+      </c>
+      <c r="E610" s="2" t="inlineStr"/>
       <c r="F610" s="3" t="n">
-        <v>51.76</v>
+        <v>56.71</v>
       </c>
       <c r="G610" s="2" t="inlineStr"/>
       <c r="H610" s="2" t="inlineStr"/>
-      <c r="I610" s="4" t="n">
-        <v>-5.3262</v>
-      </c>
-      <c r="J610" s="4" t="n">
-        <v>-4.2562</v>
-      </c>
+      <c r="I610" s="2" t="inlineStr"/>
+      <c r="J610" s="2" t="inlineStr"/>
       <c r="K610" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="L610" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST YILDIZ</t>
+          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M610" s="2" t="inlineStr"/>
@@ -26771,32 +26761,42 @@
     <row r="611">
       <c r="A611" s="6" t="inlineStr">
         <is>
-          <t>ENPRA</t>
+          <t>ARZUM</t>
         </is>
       </c>
       <c r="B611" s="7" t="n">
-        <v>70</v>
+        <v>2.41</v>
       </c>
       <c r="C611" s="8" t="n">
-        <v>-0.0515</v>
+        <v>-0.0282</v>
       </c>
       <c r="D611" s="9" t="n">
-        <v>157580</v>
-      </c>
-      <c r="E611" s="6" t="inlineStr"/>
+        <v>20190000</v>
+      </c>
+      <c r="E611" s="8" t="n">
+        <v>1</v>
+      </c>
       <c r="F611" s="7" t="n">
-        <v>9.73</v>
+        <v>32.41</v>
       </c>
       <c r="G611" s="6" t="inlineStr"/>
       <c r="H611" s="6" t="inlineStr"/>
-      <c r="I611" s="6" t="inlineStr"/>
-      <c r="J611" s="6" t="inlineStr"/>
+      <c r="I611" s="8" t="n">
+        <v>-191.6342</v>
+      </c>
+      <c r="J611" s="8" t="n">
+        <v>-0.8093</v>
+      </c>
       <c r="K611" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
-        </is>
-      </c>
-      <c r="L611" s="6" t="inlineStr"/>
+          <t>Dağıtım servisleri</t>
+        </is>
+      </c>
+      <c r="L611" s="6" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST KURUMSAL YÖNETİM</t>
+        </is>
+      </c>
       <c r="M611" s="6" t="inlineStr"/>
     </row>
   </sheetData>
@@ -26821,7 +26821,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>20.05.2026 16:30</t>
+          <t>20.05.2026 18:03</t>
         </is>
       </c>
     </row>
